--- a/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
+++ b/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="563">
   <si>
     <t>ХЯНАЛТЫН САМБАР</t>
   </si>
@@ -405,7 +405,7 @@
     <t>Захиалагч батласан талбарын толь</t>
   </si>
   <si>
-    <t>2026-09-09: 11 маягтын 1,687 талбарын эмнэлзүйн баталгаажуулалт хүлээгдэж байна (захидлын 3-р зүйл).</t>
+    <t>2026-09-09: 11 маягтын 1,687 талбарын эмнэлзүйн баталгаажуулалт хүлээгдэж байна (захидлын 3-р зүйл). | 2026-09-10: Төлөв залруулав — энэ мөр захиалагчаас хүлээгдэж байгаа тул «Дууссан» биш «Саатсан» байх ёстой (гүйцэтгэл 0%). Ажлын агуулга, хугацаа өөрчлөгдөөгүй. | 2026-09-10: Хуучин бүртгэлийн маягтуудын (AtrialRhythmNew, ICDRhythm, PaceMakerRhythm) тодорхойлолтод нэр (Label) дутуу 259 талбар илэрсэн тул баталгаажуулах хүснэгт бэлтгэв: «МнКардио_талбарын_нэр_баталгаажуулалт.xlsx». 156 талбарт кодоос санал гаргасан, 103-д нэр шинээр бичих шаардлагатай, 93 нь аль ч маягтад зурагддаггүй тул устгах эсэхийг шийдэх. Эдгээр талбар одоогоор хэвлэх, экспорт, мобайл API-д нэргүй тул гарахгүй байна.</t>
   </si>
   <si>
     <t>Динамик маягтын модуль</t>
@@ -435,7 +435,7 @@
     <t>Сервер, хандалтын эрх хүлээлгэн өгсөн</t>
   </si>
   <si>
-    <t>2026-09-09: Захиалагчийн хариу хүлээж байна — ЗСҮТ-д хүргүүлсэн захидлын 14-р зүйл.</t>
+    <t>2026-09-09: Захиалагчийн хариу хүлээж байна — ЗСҮТ-д хүргүүлсэн захидлын 14-р зүйл. | 2026-09-10: Төлөв залруулав — энэ мөр захиалагчаас хүлээгдэж байгаа тул «Дууссан» биш «Саатсан» байх ёстой (гүйцэтгэл 0%). Ажлын агуулга, хугацаа өөрчлөгдөөгүй.</t>
   </si>
   <si>
     <t>1. Мэс заслын маягтууд</t>
@@ -450,66 +450,69 @@
     <t>Талбар бүрийн нэр, төрөл, сонголтын жагсаалт, заавал бөглөх эсэх батлагдсан</t>
   </si>
   <si>
+    <t>2026-09-09: Талбарын толь, кодчилол, бөглөх дүрмийн баталгаажуулалт хүлээгдэж байна (захидлын 2, 3-р зүйл). | 2026-09-10: Төлөв залруулав — энэ мөр захиалагчаас хүлээгдэж байгаа тул «Дууссан» биш «Саатсан» байх ёстой (гүйцэтгэл 0%). Ажлын агуулга, хугацаа өөрчлөгдөөгүй.</t>
+  </si>
+  <si>
+    <t>Өгөгдлийн сангийн хүснэгт, холбоос үүсгэх</t>
+  </si>
+  <si>
+    <t>Хүснэгт, индекс, гадаад түлхүүр үүссэн, тест дата орсон</t>
+  </si>
+  <si>
+    <t>Маягтын дэлгэц (UI), CRUD, валидац хөгжүүлэх</t>
+  </si>
+  <si>
+    <t>Маягтыг нэмэх, засах, устгах, хадгалах бүрэн ажиллана; заавал талбарын шалгалт хийгдэнэ</t>
+  </si>
+  <si>
+    <t>Жагсаалт, хайлт, шүүлт, Excel экспорт</t>
+  </si>
+  <si>
+    <t>Цэсэнд жагсаалтаар харагдана; олон талбараар хайх, шүүх, .xlsx-ээр татах боломжтой</t>
+  </si>
+  <si>
+    <t>Хэвлэх маягт (A4 / PDF) боловсруулах</t>
+  </si>
+  <si>
+    <t>Батлагдсан цаасан маягттай ижил бүтэцтэй хэвлэгдэнэ</t>
+  </si>
+  <si>
+    <t>2026-09-10: A4/PDF хэвлэлт сервер тал дээр нэгдсэн үүсгэгчээр бэлэн боллоо (reports/TenderForm.js, POST /TenderForm/PrintHtml ба /TenderForm/PrintReport). Маягтын толь бичгээр удирдагддаг тул шинэ маягт нэмэхэд хэвлэлт нэмэлт кодгүйгээр ажиллана. Хоосон болон бөглөсөн хувилбартай, нөхцөлт талбарыг нуух, шалгах хуудсыг Тийм/Үгүй/Тодорхойгүй нүдэн хүснэгтээр, титэм судасны 19 сегментийг нэг хүснэгтээр хэвлэнэ. Хуудасны дугаар ба эх сурвалжийн тэмдэглэгээ (байгууллага, мэдээллийн сан, огноо) хуудасны захад гарна. Батлагдсан цаасан маягттай эцсийн тулгалт ЗСҮТ-өөс эх хувь ирсний дараа (мөр 3).</t>
+  </si>
+  <si>
+    <t>Захиалагчийн туршилт, баталгаажуулалт (UAT)</t>
+  </si>
+  <si>
+    <t>Эмч нар бодит өгөгдлөөр туршиж, санал/алдааны жагсаалт өгсөн</t>
+  </si>
+  <si>
+    <t>1.2 Мэс заслын үеийн шалгуур хуудас (аюулгүй байдлын хяналт)</t>
+  </si>
+  <si>
+    <t>2026-09-09: Маягт 1.2-ын агуулгыг тендерийн зурган хавсралтаас бүрэн буулгаж 75 талбараар ачаалав (scripts/seed_form_1_2.sql). A4 хэвлэлт TenderFormPrint.jsx-ээр ажиллана. Толь бичгийн эмнэлзүйн баталгаажуулалт үлдсэн. | 2026-09-10: A4/PDF хэвлэлт сервер тал дээр нэгдсэн үүсгэгчээр бэлэн боллоо (reports/TenderForm.js, POST /TenderForm/PrintHtml ба /TenderForm/PrintReport). Маягтын толь бичгээр удирдагддаг тул шинэ маягт нэмэхэд хэвлэлт нэмэлт кодгүйгээр ажиллана. Хоосон болон бөглөсөн хувилбартай, нөхцөлт талбарыг нуух, шалгах хуудсыг Тийм/Үгүй/Тодорхойгүй нүдэн хүснэгтээр, титэм судасны 19 сегментийг нэг хүснэгтээр хэвлэнэ. Хуудасны дугаар ба эх сурвалжийн тэмдэглэгээ (байгууллага, мэдээллийн сан, огноо) хуудасны захад гарна. Батлагдсан цаасан маягттай эцсийн тулгалт ЗСҮТ-өөс эх хувь ирсний дараа (мөр 3).</t>
+  </si>
+  <si>
+    <t>1.3 Хэвлийн гол судасны цүлхэн, гол судас-ташааны артерийн мэс заслын өмнөх шалгах хуудас</t>
+  </si>
+  <si>
+    <t>1.4 Эмнэлгээс гарах үеийн шалгуур хуудас</t>
+  </si>
+  <si>
+    <t>Гэрээ байгуулах үед тусгагдана — хамрах хүрээ тодорхой болсны дараа хугацаа шинэчлэгдэнэ | 2026-09-09: 1.4 маягтын хамрах хүрээний шийдвэр хүлээгдэж байна (захидлын 4-р зүйл).</t>
+  </si>
+  <si>
+    <t>Маягтын хөгжүүлэлт (гэрээнд тусгагдсаны дараа)</t>
+  </si>
+  <si>
+    <t>Гэрээнд тусгагдсан хүрээнд UI, CRUD, жагсаалт, хэвлэх бүрэн ажиллана</t>
+  </si>
+  <si>
+    <t>1.5 Зүрхний төрөлхийн гажгийн маягт</t>
+  </si>
+  <si>
     <t>2026-09-09: Талбарын толь, кодчилол, бөглөх дүрмийн баталгаажуулалт хүлээгдэж байна (захидлын 2, 3-р зүйл).</t>
   </si>
   <si>
-    <t>Өгөгдлийн сангийн хүснэгт, холбоос үүсгэх</t>
-  </si>
-  <si>
-    <t>Хүснэгт, индекс, гадаад түлхүүр үүссэн, тест дата орсон</t>
-  </si>
-  <si>
-    <t>Маягтын дэлгэц (UI), CRUD, валидац хөгжүүлэх</t>
-  </si>
-  <si>
-    <t>Маягтыг нэмэх, засах, устгах, хадгалах бүрэн ажиллана; заавал талбарын шалгалт хийгдэнэ</t>
-  </si>
-  <si>
-    <t>Жагсаалт, хайлт, шүүлт, Excel экспорт</t>
-  </si>
-  <si>
-    <t>Цэсэнд жагсаалтаар харагдана; олон талбараар хайх, шүүх, .xlsx-ээр татах боломжтой</t>
-  </si>
-  <si>
-    <t>Хэвлэх маягт (A4 / PDF) боловсруулах</t>
-  </si>
-  <si>
-    <t>Батлагдсан цаасан маягттай ижил бүтэцтэй хэвлэгдэнэ</t>
-  </si>
-  <si>
-    <t>2026-09-10: A4/PDF хэвлэлт сервер тал дээр нэгдсэн үүсгэгчээр бэлэн боллоо (reports/TenderForm.js, POST /TenderForm/PrintHtml ба /TenderForm/PrintReport). Маягтын толь бичгээр удирдагддаг тул шинэ маягт нэмэхэд хэвлэлт нэмэлт кодгүйгээр ажиллана. Хоосон болон бөглөсөн хувилбартай, нөхцөлт талбарыг нуух, шалгах хуудсыг Тийм/Үгүй/Тодорхойгүй нүдэн хүснэгтээр, титэм судасны 19 сегментийг нэг хүснэгтээр хэвлэнэ. Хуудасны дугаар ба эх сурвалжийн тэмдэглэгээ (байгууллага, мэдээллийн сан, огноо) хуудасны захад гарна. Батлагдсан цаасан маягттай эцсийн тулгалт ЗСҮТ-өөс эх хувь ирсний дараа (мөр 3).</t>
-  </si>
-  <si>
-    <t>Захиалагчийн туршилт, баталгаажуулалт (UAT)</t>
-  </si>
-  <si>
-    <t>Эмч нар бодит өгөгдлөөр туршиж, санал/алдааны жагсаалт өгсөн</t>
-  </si>
-  <si>
-    <t>1.2 Мэс заслын үеийн шалгуур хуудас (аюулгүй байдлын хяналт)</t>
-  </si>
-  <si>
-    <t>2026-09-09: Маягт 1.2-ын агуулгыг тендерийн зурган хавсралтаас бүрэн буулгаж 75 талбараар ачаалав (scripts/seed_form_1_2.sql). A4 хэвлэлт TenderFormPrint.jsx-ээр ажиллана. Толь бичгийн эмнэлзүйн баталгаажуулалт үлдсэн. | 2026-09-10: A4/PDF хэвлэлт сервер тал дээр нэгдсэн үүсгэгчээр бэлэн боллоо (reports/TenderForm.js, POST /TenderForm/PrintHtml ба /TenderForm/PrintReport). Маягтын толь бичгээр удирдагддаг тул шинэ маягт нэмэхэд хэвлэлт нэмэлт кодгүйгээр ажиллана. Хоосон болон бөглөсөн хувилбартай, нөхцөлт талбарыг нуух, шалгах хуудсыг Тийм/Үгүй/Тодорхойгүй нүдэн хүснэгтээр, титэм судасны 19 сегментийг нэг хүснэгтээр хэвлэнэ. Хуудасны дугаар ба эх сурвалжийн тэмдэглэгээ (байгууллага, мэдээллийн сан, огноо) хуудасны захад гарна. Батлагдсан цаасан маягттай эцсийн тулгалт ЗСҮТ-өөс эх хувь ирсний дараа (мөр 3).</t>
-  </si>
-  <si>
-    <t>1.3 Хэвлийн гол судасны цүлхэн, гол судас-ташааны артерийн мэс заслын өмнөх шалгах хуудас</t>
-  </si>
-  <si>
-    <t>1.4 Эмнэлгээс гарах үеийн шалгуур хуудас</t>
-  </si>
-  <si>
-    <t>Гэрээ байгуулах үед тусгагдана — хамрах хүрээ тодорхой болсны дараа хугацаа шинэчлэгдэнэ | 2026-09-09: 1.4 маягтын хамрах хүрээний шийдвэр хүлээгдэж байна (захидлын 4-р зүйл).</t>
-  </si>
-  <si>
-    <t>Маягтын хөгжүүлэлт (гэрээнд тусгагдсаны дараа)</t>
-  </si>
-  <si>
-    <t>Гэрээнд тусгагдсан хүрээнд UI, CRUD, жагсаалт, хэвлэх бүрэн ажиллана</t>
-  </si>
-  <si>
-    <t>1.5 Зүрхний төрөлхийн гажгийн маягт</t>
-  </si>
-  <si>
     <t>2026-09-10: A4/PDF хэвлэлт сервер тал дээр нэгдсэн үүсгэгчээр бэлэн боллоо (reports/TenderForm.js, POST /TenderForm/PrintHtml ба /TenderForm/PrintReport). Маягтын толь бичгээр удирдагддаг тул шинэ маягт нэмэхэд хэвлэлт нэмэлт кодгүйгээр ажиллана. Хоосон болон бөглөсөн хувилбартай, нөхцөлт талбарыг нуух, шалгах хуудсыг Тийм/Үгүй/Тодорхойгүй нүдэн хүснэгтээр, титэм судасны 19 сегментийг нэг хүснэгтээр хэвлэнэ. Хуудасны дугаар ба эх сурвалжийн тэмдэглэгээ (байгууллага, мэдээллийн сан, огноо) хуудасны захад гарна. Батлагдсан цаасан маягттай эцсийн тулгалт ЗСҮТ-өөс эх хувь ирсний дараа (мөр 3). Талбарын нэршил тендерийн англи эхээр байгаа тул монгол орчуулга шаардлагатай — энэ нь эмнэлзүйн нэр томьёоны ажил.</t>
   </si>
   <si>
@@ -600,7 +603,7 @@
     <t>Экспортын файл бүрэн, эх сурвалжийн тэмдэглэгээтэй</t>
   </si>
   <si>
-    <t>2026-09-10: Эх сурвалжийн тэмдэглэгээ шалгагдаж, ажиллаж байгаа нь батлагдав — SQL_DB нь config/Config.env-д тодорхойлогдсон бөгөөд server.js эхэлж уншдаг тул «Мэдээллийн сан» мөр хоосон гардаггүй. Урьд нь хоосон гэж бүртгэсэн нь эндүүрэл байв.</t>
+    <t>2026-09-10: Эх сурвалжийн тэмдэглэгээ шалгагдаж, ажиллаж байгаа нь батлагдав — SQL_DB нь config/Config.env-д тодорхойлогдсон бөгөөд server.js эхэлж уншдаг тул «Мэдээллийн сан» мөр хоосон гардаггүй. Урьд нь хоосон гэж бүртгэсэн нь эндүүрэл байв. | 2026-09-10: Эх сурвалжийн тэмдэглэгээ Excel экспортоос гадна PDF хэвлэлт БҮРТ хамаарах боллоо — helper/PrintHelper.js хуудасны доод хэсэгт байгууллага, мэдээллийн сан, огноо, хэвлэсэн хэрэглэгч, хуудасны дугаарыг гаргана. Тайлан хэвлэдэг 19 контроллерын 18 нь нэгдсэн PrintHelper-т шилжиж, тус бүр өөрийн Chrome процесс асаадаг байсныг зогсоов. Мөн тайлан бүр давхцахгүй файлын нэртэй болов: өмнө нь тогтмол нэр (Echo.pdf гэх мэт) ашигладаг байсан тул нэгэн зэрэг хэвлэсэн хоёр эмчийн файл дарж бичигдэж, нөгөө эмчлүүлэгчийн тайлан очих эрсдэлтэй байсныг арилгав.</t>
   </si>
   <si>
     <t>Иргэний хэсэг</t>
@@ -4620,7 +4623,7 @@
         <v>46209</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J23" s="23">
         <v>0</v>
@@ -4730,7 +4733,7 @@
         <v>46193</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J26" s="23">
         <v>0</v>
@@ -4768,7 +4771,7 @@
         <v>46214</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J27" s="23">
         <v>0</v>
@@ -4988,7 +4991,7 @@
         <v>46214</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J33" s="23">
         <v>0</v>
@@ -5208,7 +5211,7 @@
         <v>46220</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J39" s="23">
         <v>0</v>
@@ -5551,7 +5554,7 @@
         <v>142</v>
       </c>
       <c r="L48" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -5697,7 +5700,7 @@
         <v>151</v>
       </c>
       <c r="L52" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -5747,7 +5750,7 @@
         <v>139</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>141</v>
@@ -5771,7 +5774,7 @@
         <v>142</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -5785,7 +5788,7 @@
         <v>139</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>144</v>
@@ -5821,7 +5824,7 @@
         <v>139</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>146</v>
@@ -5857,7 +5860,7 @@
         <v>139</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>148</v>
@@ -5893,7 +5896,7 @@
         <v>139</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>150</v>
@@ -5917,7 +5920,7 @@
         <v>151</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -5931,7 +5934,7 @@
         <v>139</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>153</v>
@@ -5967,7 +5970,7 @@
         <v>139</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>141</v>
@@ -5991,7 +5994,7 @@
         <v>142</v>
       </c>
       <c r="L60" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6005,7 +6008,7 @@
         <v>139</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>144</v>
@@ -6041,7 +6044,7 @@
         <v>139</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>146</v>
@@ -6077,7 +6080,7 @@
         <v>139</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>148</v>
@@ -6113,7 +6116,7 @@
         <v>139</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E64" s="19" t="s">
         <v>150</v>
@@ -6137,7 +6140,7 @@
         <v>151</v>
       </c>
       <c r="L64" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6151,7 +6154,7 @@
         <v>139</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E65" s="19" t="s">
         <v>153</v>
@@ -6187,7 +6190,7 @@
         <v>139</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E66" s="19" t="s">
         <v>141</v>
@@ -6211,7 +6214,7 @@
         <v>142</v>
       </c>
       <c r="L66" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6225,7 +6228,7 @@
         <v>139</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E67" s="19" t="s">
         <v>144</v>
@@ -6261,7 +6264,7 @@
         <v>139</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E68" s="19" t="s">
         <v>146</v>
@@ -6297,7 +6300,7 @@
         <v>139</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E69" s="19" t="s">
         <v>148</v>
@@ -6333,7 +6336,7 @@
         <v>139</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>150</v>
@@ -6357,7 +6360,7 @@
         <v>151</v>
       </c>
       <c r="L70" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6371,7 +6374,7 @@
         <v>139</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>153</v>
@@ -6407,7 +6410,7 @@
         <v>139</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>141</v>
@@ -6431,7 +6434,7 @@
         <v>142</v>
       </c>
       <c r="L72" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6445,7 +6448,7 @@
         <v>139</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>144</v>
@@ -6481,7 +6484,7 @@
         <v>139</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>146</v>
@@ -6517,7 +6520,7 @@
         <v>139</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>148</v>
@@ -6553,7 +6556,7 @@
         <v>139</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>150</v>
@@ -6577,7 +6580,7 @@
         <v>151</v>
       </c>
       <c r="L76" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6591,7 +6594,7 @@
         <v>139</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>153</v>
@@ -6627,7 +6630,7 @@
         <v>139</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>141</v>
@@ -6651,7 +6654,7 @@
         <v>142</v>
       </c>
       <c r="L78" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6665,7 +6668,7 @@
         <v>139</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>144</v>
@@ -6689,7 +6692,7 @@
         <v>145</v>
       </c>
       <c r="L79" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6703,7 +6706,7 @@
         <v>139</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E80" s="19" t="s">
         <v>160</v>
@@ -6727,7 +6730,7 @@
         <v>161</v>
       </c>
       <c r="L80" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6738,10 +6741,10 @@
         <v>28</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>141</v>
@@ -6765,7 +6768,7 @@
         <v>142</v>
       </c>
       <c r="L81" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6776,10 +6779,10 @@
         <v>28</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>144</v>
@@ -6812,10 +6815,10 @@
         <v>28</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>146</v>
@@ -6848,10 +6851,10 @@
         <v>28</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>148</v>
@@ -6884,10 +6887,10 @@
         <v>28</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>150</v>
@@ -6922,10 +6925,10 @@
         <v>28</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>153</v>
@@ -6958,10 +6961,10 @@
         <v>28</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>141</v>
@@ -6985,7 +6988,7 @@
         <v>142</v>
       </c>
       <c r="L87" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6996,10 +6999,10 @@
         <v>28</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>144</v>
@@ -7023,7 +7026,7 @@
         <v>145</v>
       </c>
       <c r="L88" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7034,10 +7037,10 @@
         <v>28</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>146</v>
@@ -7061,7 +7064,7 @@
         <v>147</v>
       </c>
       <c r="L89" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7072,10 +7075,10 @@
         <v>28</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E90" s="19" t="s">
         <v>148</v>
@@ -7099,7 +7102,7 @@
         <v>149</v>
       </c>
       <c r="L90" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7110,10 +7113,10 @@
         <v>28</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E91" s="19" t="s">
         <v>150</v>
@@ -7137,7 +7140,7 @@
         <v>151</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7148,10 +7151,10 @@
         <v>28</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E92" s="19" t="s">
         <v>153</v>
@@ -7175,7 +7178,7 @@
         <v>154</v>
       </c>
       <c r="L92" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7186,10 +7189,10 @@
         <v>28</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E93" s="19" t="s">
         <v>141</v>
@@ -7213,7 +7216,7 @@
         <v>142</v>
       </c>
       <c r="L93" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7224,10 +7227,10 @@
         <v>28</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>144</v>
@@ -7260,10 +7263,10 @@
         <v>28</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E95" s="19" t="s">
         <v>146</v>
@@ -7296,10 +7299,10 @@
         <v>28</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E96" s="19" t="s">
         <v>148</v>
@@ -7323,7 +7326,7 @@
         <v>149</v>
       </c>
       <c r="L96" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7334,10 +7337,10 @@
         <v>28</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E97" s="19" t="s">
         <v>150</v>
@@ -7372,10 +7375,10 @@
         <v>28</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E98" s="19" t="s">
         <v>153</v>
@@ -7408,10 +7411,10 @@
         <v>28</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>141</v>
@@ -7435,7 +7438,7 @@
         <v>142</v>
       </c>
       <c r="L99" s="19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7446,10 +7449,10 @@
         <v>28</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>144</v>
@@ -7482,10 +7485,10 @@
         <v>28</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>146</v>
@@ -7518,10 +7521,10 @@
         <v>28</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E102" s="19" t="s">
         <v>148</v>
@@ -7545,7 +7548,7 @@
         <v>149</v>
       </c>
       <c r="L102" s="19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7556,10 +7559,10 @@
         <v>28</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E103" s="19" t="s">
         <v>150</v>
@@ -7583,7 +7586,7 @@
         <v>151</v>
       </c>
       <c r="L103" s="19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7594,10 +7597,10 @@
         <v>28</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E104" s="19" t="s">
         <v>153</v>
@@ -7630,13 +7633,13 @@
         <v>28</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F105" s="17" t="s">
         <v>16</v>
@@ -7654,7 +7657,7 @@
         <v>1</v>
       </c>
       <c r="K105" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L105" s="19"/>
     </row>
@@ -7666,13 +7669,13 @@
         <v>28</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F106" s="17" t="s">
         <v>16</v>
@@ -7690,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="K106" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L106" s="19"/>
     </row>
@@ -7702,13 +7705,13 @@
         <v>28</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F107" s="17" t="s">
         <v>16</v>
@@ -7726,10 +7729,10 @@
         <v>1</v>
       </c>
       <c r="K107" s="19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L107" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7740,13 +7743,13 @@
         <v>28</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F108" s="17" t="s">
         <v>16</v>
@@ -7764,10 +7767,10 @@
         <v>1</v>
       </c>
       <c r="K108" s="19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L108" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7778,13 +7781,13 @@
         <v>28</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F109" s="17" t="s">
         <v>17</v>
@@ -7802,10 +7805,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L109" s="19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7816,13 +7819,13 @@
         <v>28</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F110" s="17" t="s">
         <v>16</v>
@@ -7840,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L110" s="19"/>
     </row>
@@ -7852,13 +7855,13 @@
         <v>28</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F111" s="17" t="s">
         <v>16</v>
@@ -7876,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L111" s="19"/>
     </row>
@@ -7888,13 +7891,13 @@
         <v>28</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F112" s="17" t="s">
         <v>17</v>
@@ -7912,10 +7915,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L112" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7926,13 +7929,13 @@
         <v>28</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F113" s="17" t="s">
         <v>16</v>
@@ -7950,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L113" s="19"/>
     </row>
@@ -7962,13 +7965,13 @@
         <v>28</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F114" s="17" t="s">
         <v>16</v>
@@ -7986,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L114" s="19"/>
     </row>
@@ -7998,13 +8001,13 @@
         <v>28</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F115" s="17" t="s">
         <v>17</v>
@@ -8022,7 +8025,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L115" s="19"/>
     </row>
@@ -8034,13 +8037,13 @@
         <v>28</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F116" s="17" t="s">
         <v>16</v>
@@ -8058,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L116" s="19"/>
     </row>
@@ -8070,13 +8073,13 @@
         <v>28</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F117" s="17" t="s">
         <v>16</v>
@@ -8094,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L117" s="19"/>
     </row>
@@ -8106,13 +8109,13 @@
         <v>28</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F118" s="17" t="s">
         <v>17</v>
@@ -8130,10 +8133,10 @@
         <v>0</v>
       </c>
       <c r="K118" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L118" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8144,13 +8147,13 @@
         <v>28</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F119" s="17" t="s">
         <v>16</v>
@@ -8168,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L119" s="19"/>
     </row>
@@ -8180,13 +8183,13 @@
         <v>28</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F120" s="17" t="s">
         <v>16</v>
@@ -8204,7 +8207,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L120" s="19"/>
     </row>
@@ -8216,13 +8219,13 @@
         <v>28</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F121" s="17" t="s">
         <v>17</v>
@@ -8240,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L121" s="19"/>
     </row>
@@ -8252,13 +8255,13 @@
         <v>28</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F122" s="17" t="s">
         <v>16</v>
@@ -8276,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L122" s="19"/>
     </row>
@@ -8288,13 +8291,13 @@
         <v>28</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F123" s="17" t="s">
         <v>16</v>
@@ -8312,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L123" s="19"/>
     </row>
@@ -8324,13 +8327,13 @@
         <v>28</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F124" s="17" t="s">
         <v>17</v>
@@ -8348,7 +8351,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L124" s="19"/>
     </row>
@@ -8360,13 +8363,13 @@
         <v>28</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F125" s="17" t="s">
         <v>16</v>
@@ -8384,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L125" s="19"/>
     </row>
@@ -8396,13 +8399,13 @@
         <v>28</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D126" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F126" s="17" t="s">
         <v>16</v>
@@ -8420,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L126" s="19"/>
     </row>
@@ -8432,13 +8435,13 @@
         <v>28</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F127" s="17" t="s">
         <v>17</v>
@@ -8456,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L127" s="19"/>
     </row>
@@ -8468,13 +8471,13 @@
         <v>28</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D128" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F128" s="17" t="s">
         <v>16</v>
@@ -8492,7 +8495,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L128" s="19"/>
     </row>
@@ -8504,13 +8507,13 @@
         <v>28</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>16</v>
@@ -8528,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L129" s="19"/>
     </row>
@@ -8540,13 +8543,13 @@
         <v>28</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D130" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E130" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F130" s="17" t="s">
         <v>17</v>
@@ -8564,7 +8567,7 @@
         <v>0</v>
       </c>
       <c r="K130" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L130" s="19"/>
     </row>
@@ -8576,13 +8579,13 @@
         <v>28</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D131" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F131" s="17" t="s">
         <v>16</v>
@@ -8600,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L131" s="19"/>
     </row>
@@ -8612,13 +8615,13 @@
         <v>28</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F132" s="17" t="s">
         <v>16</v>
@@ -8636,7 +8639,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L132" s="19"/>
     </row>
@@ -8648,13 +8651,13 @@
         <v>28</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>16</v>
@@ -8672,7 +8675,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L133" s="19"/>
     </row>
@@ -8684,13 +8687,13 @@
         <v>28</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D134" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E134" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F134" s="17" t="s">
         <v>16</v>
@@ -8708,7 +8711,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L134" s="19"/>
     </row>
@@ -8720,13 +8723,13 @@
         <v>30</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F135" s="17" t="s">
         <v>16</v>
@@ -8744,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L135" s="19"/>
     </row>
@@ -8756,13 +8759,13 @@
         <v>30</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F136" s="17" t="s">
         <v>16</v>
@@ -8780,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L136" s="19"/>
     </row>
@@ -8792,13 +8795,13 @@
         <v>30</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D137" s="19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E137" s="19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F137" s="17" t="s">
         <v>16</v>
@@ -8816,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L137" s="19"/>
     </row>
@@ -8828,13 +8831,13 @@
         <v>30</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D138" s="19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E138" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F138" s="17" t="s">
         <v>17</v>
@@ -8852,7 +8855,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L138" s="19"/>
     </row>
@@ -8864,13 +8867,13 @@
         <v>30</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D139" s="19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E139" s="19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F139" s="17" t="s">
         <v>17</v>
@@ -8888,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="K139" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L139" s="19"/>
     </row>
@@ -8900,13 +8903,13 @@
         <v>30</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D140" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F140" s="17" t="s">
         <v>16</v>
@@ -8924,7 +8927,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L140" s="19"/>
     </row>
@@ -8936,13 +8939,13 @@
         <v>30</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D141" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E141" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F141" s="17" t="s">
         <v>17</v>
@@ -8960,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L141" s="19"/>
     </row>
@@ -8972,13 +8975,13 @@
         <v>30</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D142" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E142" s="19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F142" s="17" t="s">
         <v>16</v>
@@ -8996,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L142" s="19"/>
     </row>
@@ -9008,13 +9011,13 @@
         <v>30</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D143" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E143" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F143" s="17" t="s">
         <v>16</v>
@@ -9032,7 +9035,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L143" s="19"/>
     </row>
@@ -9044,13 +9047,13 @@
         <v>32</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E144" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F144" s="17" t="s">
         <v>16</v>
@@ -9068,7 +9071,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L144" s="19"/>
     </row>
@@ -9080,13 +9083,13 @@
         <v>32</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D145" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E145" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F145" s="17" t="s">
         <v>16</v>
@@ -9104,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="K145" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L145" s="19"/>
     </row>
@@ -9116,13 +9119,13 @@
         <v>32</v>
       </c>
       <c r="C146" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E146" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F146" s="17" t="s">
         <v>16</v>
@@ -9140,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L146" s="19"/>
     </row>
@@ -9152,13 +9155,13 @@
         <v>32</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D147" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E147" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F147" s="17" t="s">
         <v>16</v>
@@ -9176,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L147" s="19"/>
     </row>
@@ -9188,13 +9191,13 @@
         <v>32</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D148" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E148" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F148" s="17" t="s">
         <v>17</v>
@@ -9212,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L148" s="19"/>
     </row>
@@ -9224,13 +9227,13 @@
         <v>32</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D149" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E149" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F149" s="17" t="s">
         <v>16</v>
@@ -9248,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L149" s="19"/>
     </row>
@@ -9260,13 +9263,13 @@
         <v>34</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D150" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E150" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F150" s="17" t="s">
         <v>16</v>
@@ -9284,7 +9287,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L150" s="19"/>
     </row>
@@ -9296,13 +9299,13 @@
         <v>34</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D151" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F151" s="17" t="s">
         <v>16</v>
@@ -9320,7 +9323,7 @@
         <v>0</v>
       </c>
       <c r="K151" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L151" s="19"/>
     </row>
@@ -9332,13 +9335,13 @@
         <v>34</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D152" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E152" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F152" s="17" t="s">
         <v>17</v>
@@ -9356,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="K152" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L152" s="19"/>
     </row>
@@ -9368,13 +9371,13 @@
         <v>34</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D153" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E153" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F153" s="17" t="s">
         <v>16</v>
@@ -9392,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="K153" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L153" s="19"/>
     </row>
@@ -9404,13 +9407,13 @@
         <v>34</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D154" s="19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E154" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F154" s="17" t="s">
         <v>17</v>
@@ -9428,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="K154" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L154" s="19"/>
     </row>
@@ -9440,13 +9443,13 @@
         <v>36</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D155" s="19" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E155" s="19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F155" s="17" t="s">
         <v>16</v>
@@ -9464,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L155" s="19"/>
     </row>
@@ -9476,13 +9479,13 @@
         <v>36</v>
       </c>
       <c r="C156" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D156" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E156" s="19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F156" s="17" t="s">
         <v>16</v>
@@ -9500,7 +9503,7 @@
         <v>0</v>
       </c>
       <c r="K156" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L156" s="19"/>
     </row>
@@ -9512,13 +9515,13 @@
         <v>36</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D157" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E157" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F157" s="17" t="s">
         <v>17</v>
@@ -9536,7 +9539,7 @@
         <v>0</v>
       </c>
       <c r="K157" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L157" s="19"/>
     </row>
@@ -10505,13 +10508,13 @@
         <v>39</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>16</v>
@@ -10529,10 +10532,10 @@
         <v>1</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10543,13 +10546,13 @@
         <v>39</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>16</v>
@@ -10567,10 +10570,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10581,13 +10584,13 @@
         <v>39</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>16</v>
@@ -10605,10 +10608,10 @@
         <v>1</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10619,13 +10622,13 @@
         <v>39</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>17</v>
@@ -10643,7 +10646,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L8" s="19" t="s">
         <v>101</v>
@@ -10657,13 +10660,13 @@
         <v>39</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>16</v>
@@ -10681,10 +10684,10 @@
         <v>1</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10695,13 +10698,13 @@
         <v>39</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>17</v>
@@ -10719,10 +10722,10 @@
         <v>1</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10733,13 +10736,13 @@
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>16</v>
@@ -10757,10 +10760,10 @@
         <v>1</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10771,13 +10774,13 @@
         <v>41</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>16</v>
@@ -10795,10 +10798,10 @@
         <v>1</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10809,13 +10812,13 @@
         <v>41</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>16</v>
@@ -10833,10 +10836,10 @@
         <v>1</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10847,13 +10850,13 @@
         <v>41</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>16</v>
@@ -10871,10 +10874,10 @@
         <v>1</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L14" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10885,13 +10888,13 @@
         <v>41</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>17</v>
@@ -10909,10 +10912,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L15" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10923,13 +10926,13 @@
         <v>43</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>16</v>
@@ -10947,10 +10950,10 @@
         <v>1</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10961,13 +10964,13 @@
         <v>43</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>16</v>
@@ -10985,10 +10988,10 @@
         <v>1</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -10999,13 +11002,13 @@
         <v>43</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>16</v>
@@ -11023,10 +11026,10 @@
         <v>0</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -11037,13 +11040,13 @@
         <v>43</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>16</v>
@@ -11061,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L19" s="19"/>
     </row>
@@ -11073,13 +11076,13 @@
         <v>43</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>16</v>
@@ -11097,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L20" s="19"/>
     </row>
@@ -11109,13 +11112,13 @@
         <v>43</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>16</v>
@@ -11133,7 +11136,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L21" s="19"/>
     </row>
@@ -11145,13 +11148,13 @@
         <v>43</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>16</v>
@@ -11169,7 +11172,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L22" s="19"/>
     </row>
@@ -11181,13 +11184,13 @@
         <v>43</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>16</v>
@@ -11205,7 +11208,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L23" s="19"/>
     </row>
@@ -11217,13 +11220,13 @@
         <v>43</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>16</v>
@@ -11241,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L24" s="19"/>
     </row>
@@ -11253,13 +11256,13 @@
         <v>43</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>16</v>
@@ -11277,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L25" s="19"/>
     </row>
@@ -11289,13 +11292,13 @@
         <v>43</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>17</v>
@@ -11313,7 +11316,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L26" s="19" t="s">
         <v>94</v>
@@ -11327,13 +11330,13 @@
         <v>43</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>16</v>
@@ -11351,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L27" s="19"/>
     </row>
@@ -11363,13 +11366,13 @@
         <v>43</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>16</v>
@@ -11387,10 +11390,10 @@
         <v>0</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11401,13 +11404,13 @@
         <v>43</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>16</v>
@@ -11425,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L29" s="19"/>
     </row>
@@ -11437,13 +11440,13 @@
         <v>43</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>16</v>
@@ -11461,7 +11464,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L30" s="19"/>
     </row>
@@ -11473,13 +11476,13 @@
         <v>43</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>16</v>
@@ -11497,7 +11500,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L31" s="19"/>
     </row>
@@ -11509,13 +11512,13 @@
         <v>45</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>16</v>
@@ -11533,7 +11536,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L32" s="19"/>
     </row>
@@ -11545,13 +11548,13 @@
         <v>45</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>16</v>
@@ -11569,7 +11572,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L33" s="19"/>
     </row>
@@ -11581,13 +11584,13 @@
         <v>45</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>16</v>
@@ -11605,7 +11608,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L34" s="19"/>
     </row>
@@ -11617,13 +11620,13 @@
         <v>45</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>16</v>
@@ -11641,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L35" s="19"/>
     </row>
@@ -11653,13 +11656,13 @@
         <v>45</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>16</v>
@@ -11677,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L36" s="19"/>
     </row>
@@ -11689,13 +11692,13 @@
         <v>45</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>17</v>
@@ -11713,7 +11716,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L37" s="19"/>
     </row>
@@ -11725,13 +11728,13 @@
         <v>47</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>16</v>
@@ -11749,7 +11752,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="19" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L38" s="19"/>
     </row>
@@ -11761,13 +11764,13 @@
         <v>47</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>16</v>
@@ -11785,7 +11788,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L39" s="19"/>
     </row>
@@ -11797,13 +11800,13 @@
         <v>47</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>16</v>
@@ -11821,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L40" s="19"/>
     </row>
@@ -11833,13 +11836,13 @@
         <v>47</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>16</v>
@@ -11857,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L41" s="19"/>
     </row>
@@ -11869,13 +11872,13 @@
         <v>47</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>17</v>
@@ -11893,10 +11896,10 @@
         <v>0</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L42" s="19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11907,13 +11910,13 @@
         <v>47</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>16</v>
@@ -11931,7 +11934,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L43" s="19"/>
     </row>
@@ -11943,13 +11946,13 @@
         <v>47</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>16</v>
@@ -11967,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L44" s="19"/>
     </row>
@@ -11979,13 +11982,13 @@
         <v>47</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>16</v>
@@ -12003,7 +12006,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L45" s="19"/>
     </row>
@@ -12015,13 +12018,13 @@
         <v>49</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>16</v>
@@ -12039,7 +12042,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L46" s="19"/>
     </row>
@@ -12051,13 +12054,13 @@
         <v>49</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>16</v>
@@ -12075,7 +12078,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L47" s="19"/>
     </row>
@@ -12087,13 +12090,13 @@
         <v>49</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>16</v>
@@ -12111,7 +12114,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L48" s="19"/>
     </row>
@@ -12123,13 +12126,13 @@
         <v>49</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>16</v>
@@ -12147,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="19" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L49" s="19"/>
     </row>
@@ -12159,13 +12162,13 @@
         <v>49</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>16</v>
@@ -12183,7 +12186,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L50" s="19"/>
     </row>
@@ -12195,13 +12198,13 @@
         <v>49</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>16</v>
@@ -12219,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L51" s="19"/>
     </row>
@@ -12231,13 +12234,13 @@
         <v>49</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>16</v>
@@ -12255,7 +12258,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L52" s="19"/>
     </row>
@@ -12267,13 +12270,13 @@
         <v>49</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>16</v>
@@ -12291,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L53" s="19"/>
     </row>
@@ -12303,13 +12306,13 @@
         <v>49</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>16</v>
@@ -12327,7 +12330,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L54" s="19"/>
     </row>
@@ -12339,13 +12342,13 @@
         <v>49</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>16</v>
@@ -12363,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L55" s="19"/>
     </row>
@@ -12375,13 +12378,13 @@
         <v>49</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>16</v>
@@ -12399,7 +12402,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L56" s="19"/>
     </row>
@@ -12411,13 +12414,13 @@
         <v>49</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>16</v>
@@ -12435,10 +12438,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12449,13 +12452,13 @@
         <v>49</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>17</v>
@@ -12473,10 +12476,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12487,13 +12490,13 @@
         <v>49</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>16</v>
@@ -12511,10 +12514,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12525,13 +12528,13 @@
         <v>49</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>16</v>
@@ -12549,10 +12552,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="19" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L60" s="19" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12563,13 +12566,13 @@
         <v>51</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>16</v>
@@ -12587,7 +12590,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L61" s="19"/>
     </row>
@@ -12599,13 +12602,13 @@
         <v>51</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>16</v>
@@ -12623,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L62" s="19"/>
     </row>
@@ -12635,13 +12638,13 @@
         <v>51</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>17</v>
@@ -12659,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="19" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L63" s="19"/>
     </row>
@@ -12671,13 +12674,13 @@
         <v>51</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>16</v>
@@ -12695,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L64" s="19"/>
     </row>
@@ -12707,13 +12710,13 @@
         <v>51</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>16</v>
@@ -12731,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L65" s="19"/>
     </row>
@@ -12743,13 +12746,13 @@
         <v>51</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>16</v>
@@ -12767,7 +12770,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L66" s="19"/>
     </row>
@@ -12779,13 +12782,13 @@
         <v>51</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>16</v>
@@ -12803,7 +12806,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L67" s="19"/>
     </row>
@@ -12815,13 +12818,13 @@
         <v>51</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>16</v>
@@ -12839,7 +12842,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L68" s="19"/>
     </row>
@@ -12851,13 +12854,13 @@
         <v>53</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>16</v>
@@ -12875,7 +12878,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L69" s="19"/>
     </row>
@@ -12887,13 +12890,13 @@
         <v>53</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>16</v>
@@ -12911,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L70" s="19"/>
     </row>
@@ -12923,13 +12926,13 @@
         <v>53</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>17</v>
@@ -12947,7 +12950,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L71" s="19"/>
     </row>
@@ -12959,13 +12962,13 @@
         <v>53</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F72" s="17" t="s">
         <v>17</v>
@@ -12983,7 +12986,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="19" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L72" s="19"/>
     </row>
@@ -12995,13 +12998,13 @@
         <v>53</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>17</v>
@@ -13019,7 +13022,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L73" s="19"/>
     </row>
@@ -13031,13 +13034,13 @@
         <v>53</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>16</v>
@@ -13055,7 +13058,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L74" s="19"/>
     </row>
@@ -13067,13 +13070,13 @@
         <v>55</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>17</v>
@@ -13091,7 +13094,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="19" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L75" s="19"/>
     </row>
@@ -13103,13 +13106,13 @@
         <v>55</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>16</v>
@@ -13127,7 +13130,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="19" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L76" s="19"/>
     </row>
@@ -13139,13 +13142,13 @@
         <v>55</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>16</v>
@@ -13163,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L77" s="19"/>
     </row>
@@ -13175,13 +13178,13 @@
         <v>55</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>16</v>
@@ -13199,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L78" s="19"/>
     </row>
@@ -13211,13 +13214,13 @@
         <v>55</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>16</v>
@@ -13235,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L79" s="19"/>
     </row>
@@ -13247,13 +13250,13 @@
         <v>57</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>16</v>
@@ -13271,7 +13274,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L80" s="19"/>
     </row>
@@ -13283,13 +13286,13 @@
         <v>57</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F81" s="17" t="s">
         <v>16</v>
@@ -13307,7 +13310,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L81" s="19"/>
     </row>
@@ -13319,13 +13322,13 @@
         <v>57</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F82" s="17" t="s">
         <v>16</v>
@@ -13343,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="19" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L82" s="19"/>
     </row>
@@ -13355,13 +13358,13 @@
         <v>57</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F83" s="17" t="s">
         <v>17</v>
@@ -13379,7 +13382,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="19" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L83" s="19"/>
     </row>
@@ -13391,13 +13394,13 @@
         <v>57</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>17</v>
@@ -13415,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="19" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L84" s="19"/>
     </row>
@@ -13427,13 +13430,13 @@
         <v>57</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>16</v>
@@ -13451,7 +13454,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L85" s="19"/>
     </row>
@@ -13463,13 +13466,13 @@
         <v>57</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>17</v>
@@ -13487,7 +13490,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L86" s="19"/>
     </row>

--- a/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
+++ b/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="748">
   <si>
     <t>ХЯНАЛТЫН САМБАР</t>
   </si>
@@ -406,7 +406,7 @@
     <t>Захиалагч батласан талбарын толь</t>
   </si>
   <si>
-    <t>2026-09-09: 11 маягтын 1,687 талбарын эмнэлзүйн баталгаажуулалт хүлээгдэж байна (захидлын 3-р зүйл). | 2026-09-10: Төлөв залруулав — энэ мөр захиалагчаас хүлээгдэж байгаа тул «Дууссан» биш «Саатсан» байх ёстой (гүйцэтгэл 0%). Ажлын агуулга, хугацаа өөрчлөгдөөгүй. | 2026-09-10: Хуучин бүртгэлийн маягтуудын (AtrialRhythmNew, ICDRhythm, PaceMakerRhythm) тодорхойлолтод нэр (Label) дутуу 259 талбар илэрсэн тул баталгаажуулах хүснэгт бэлтгэв: «МнКардио_талбарын_нэр_баталгаажуулалт.xlsx». 156 талбарт кодоос санал гаргасан, 103-д нэр шинээр бичих шаардлагатай, 93 нь аль ч маягтад зурагддаггүй тул устгах эсэхийг шийдэх. Эдгээр талбар одоогоор хэвлэх, экспорт, мобайл API-д нэргүй тул гарахгүй байна.</t>
+    <t>2026-09-09: 11 маягтын 1,687 талбарын эмнэлзүйн баталгаажуулалт хүлээгдэж байна (захидлын 3-р зүйл). | 2026-09-10: Төлөв залруулав — энэ мөр захиалагчаас хүлээгдэж байгаа тул «Дууссан» биш «Саатсан» байх ёстой (гүйцэтгэл 0%). Ажлын агуулга, хугацаа өөрчлөгдөөгүй. | 2026-09-10: Хуучин бүртгэлийн маягтуудын (AtrialRhythmNew, ICDRhythm, PaceMakerRhythm) тодорхойлолтод нэр (Label) дутуу 259 талбар илэрсэн тул баталгаажуулах хүснэгт бэлтгэв: «МнКардио_талбарын_нэр_баталгаажуулалт.xlsx». 156 талбарт кодоос санал гаргасан, 103-д нэр шинээр бичих шаардлагатай, 93 нь аль ч маягтад зурагддаггүй тул устгах эсэхийг шийдэх. Эдгээр талбар одоогоор хэвлэх, экспорт, мобайл API-д нэргүй тул гарахгүй байна. | 2026-09-11: Нэмэлт тодруулах 12 асуудлыг ZSUT-followup-2026-09-11.md-д жагсаав (шошго дахь хөгжүүлэгчийн заавар, 3.1-ийн заавал талбар, HAS-BLED, MoCA хавсралт г.м.).</t>
   </si>
   <si>
     <t>Динамик маягтын модуль</t>
@@ -466,6 +466,9 @@
     <t>Маягтыг нэмэх, засах, устгах, хадгалах бүрэн ажиллана; заавал талбарын шалгалт хийгдэнэ</t>
   </si>
   <si>
+    <t>2026-09-11: Маягтын хөдөлгүүрийн засвар: баталгаажсан бүртгэлийг сервер талд хэн ч засах, устгах боломжгүй (тендер 3.1 L8599-8605); өөр байгууллагын бүртгэлийг засах/баталгаажуулах/устгахыг хориглосон (админаас бусад); «Дуусгаж хадгалах» товч; баталгаажуулахад заавал талбарыг сервер шалгана; тоо/огнооны утгыг шалгана; нөхцөлт талбарын дүрэм (a|b, !x, дамжих) дэлгэц, хэвлэлт хоёрт нэг. backend 241393b, frontend 007266b; туршилтын орчинд байршуулсан. Шалгалт: API 20/20, хөтөч 20/20.</t>
+  </si>
+  <si>
     <t>Жагсаалт, хайлт, шүүлт, Excel экспорт</t>
   </si>
   <si>
@@ -523,6 +526,9 @@
     <t>1.7 Гол судасны мэс заслын маягт</t>
   </si>
   <si>
+    <t>2026-09-11: Маягтын хөдөлгүүрийн засвар: баталгаажсан бүртгэлийг сервер талд хэн ч засах, устгах боломжгүй (тендер 3.1 L8599-8605); өөр байгууллагын бүртгэлийг засах/баталгаажуулах/устгахыг хориглосон (админаас бусад); «Дуусгаж хадгалах» товч; баталгаажуулахад заавал талбарыг сервер шалгана; тоо/огнооны утгыг шалгана; нөхцөлт талбарын дүрэм (a|b, !x, дамжих) дэлгэц, хэвлэлт хоёрт нэг. backend 241393b, frontend 007266b; туршилтын орчинд байршуулсан. Шалгалт: API 20/20, хөтөч 20/20. 1.7: «Blood transfusion after surgery until discharge» асуулт талбар дутуу байсныг нэмэв (scripts/fix_form_conditional_links_and_sections.sql).</t>
+  </si>
+  <si>
     <t>1.8 Хавхлагын мэс заслын маягт</t>
   </si>
   <si>
@@ -550,6 +556,9 @@
     <t>Хамгийн том маягт — үзлэг, асуумж, бодит үзлэг, багаж/лаб шинжилгээ, эмийн хэрэглээ, интервеншн, хүндрэл гэсэн 12+ хэсэгтэй</t>
   </si>
   <si>
+    <t>Хамгийн том маягт — үзлэг, асуумж, бодит үзлэг, багаж/лаб шинжилгээ, эмийн хэрэглээ, интервеншн, хүндрэл гэсэн 12+ хэсэгтэй | 2026-09-11: Маягтын хөдөлгүүрийн засвар: баталгаажсан бүртгэлийг сервер талд хэн ч засах, устгах боломжгүй (тендер 3.1 L8599-8605); өөр байгууллагын бүртгэлийг засах/баталгаажуулах/устгахыг хориглосон (админаас бусад); «Дуусгаж хадгалах» товч; баталгаажуулахад заавал талбарыг сервер шалгана; тоо/огнооны утгыг шалгана; нөхцөлт талбарын дүрэм (a|b, !x, дамжих) дэлгэц, хэвлэлт хоёрт нэг. backend 241393b, frontend 007266b; туршилтын орчинд байршуулсан. Шалгалт: API 20/20, хөтөч 20/20. 2.2: CHADS2-VASc оноо автоматаар тооцогдоно; «Тийм бол» 9 талбар эцэг асуулттайгаа холбогдов (өмнө 0); сонголт хэлбэрээр гарсан 11 огноо, 12 хэмжилт огноо/тоон талбар болов; эмийн жагсаалт «Тийм» сонголттой болов.</t>
+  </si>
+  <si>
     <t>Хамгийн том маягт — үзлэг, асуумж, бодит үзлэг, багаж/лаб шинжилгээ, эмийн хэрэглээ, интервеншн, хүндрэл гэсэн 12+ хэсэгтэй | 2026-09-10: A4/PDF хэвлэлт сервер тал дээр нэгдсэн үүсгэгчээр бэлэн боллоо (reports/TenderForm.js, POST /TenderForm/PrintHtml ба /TenderForm/PrintReport). Маягтын толь бичгээр удирдагддаг тул шинэ маягт нэмэхэд хэвлэлт нэмэлт кодгүйгээр ажиллана. Хоосон болон бөглөсөн хувилбартай, нөхцөлт талбарыг нуух, шалгах хуудсыг Тийм/Үгүй/Тодорхойгүй нүдэн хүснэгтээр, титэм судасны 19 сегментийг нэг хүснэгтээр хэвлэнэ. Хуудасны дугаар ба эх сурвалжийн тэмдэглэгээ (байгууллага, мэдээллийн сан, огноо) хуудасны захад гарна. Батлагдсан цаасан маягттай эцсийн тулгалт ЗСҮТ-өөс эх хувь ирсний дараа (мөр 3).</t>
   </si>
   <si>
@@ -559,9 +568,15 @@
     <t>3.1 Титэм судасны оношилгоо эмчилгээний маягт</t>
   </si>
   <si>
+    <t>2026-09-11: Маягтын хөдөлгүүрийн засвар: баталгаажсан бүртгэлийг сервер талд хэн ч засах, устгах боломжгүй (тендер 3.1 L8599-8605); өөр байгууллагын бүртгэлийг засах/баталгаажуулах/устгахыг хориглосон (админаас бусад); «Дуусгаж хадгалах» товч; баталгаажуулахад заавал талбарыг сервер шалгана; тоо/огнооны утгыг шалгана; нөхцөлт талбарын дүрэм (a|b, !x, дамжих) дэлгэц, хэвлэлт хоёрт нэг. backend 241393b, frontend 007266b; туршилтын орчинд байршуулсан. Шалгалт: API 20/20, хөтөч 20/20. 3.1: «Coronary angiography only» сонгоход Ангиопласти хэсгүүд алгасагдана (L8330); ST+ бүртгэлийн хэсэг ACS ST+ үед гарна (L8492); давтан ажилбарт «Өмнөх мэдээллийг хуулах уу?» — огноо, цаг хуулагдахгүй (L8175); Pain-ECG, ECG-wire, ECG-TIV минутаар тооцогдоно (L8594); нөхцөлт талбар 18 -&gt; 63.</t>
+  </si>
+  <si>
     <t>2026-09-10: Жагсаалтын багана засварлав: 3.1 маягт IsSearchable талбаргүй байсан тул сүлжээнд зөвхөн үндсэн багана харагдаж байв. AnginaStatus, CharacterOfExamination, ResultConclusion, DecisionForCAG-г тэмдэглэв (scripts/set_form_searchable_fields.sql). Тус скриптийн хамгаалалтын алдааг мөн зассан.</t>
   </si>
   <si>
+    <t>2026-09-10: A4/PDF хэвлэлт сервер тал дээр нэгдсэн үүсгэгчээр бэлэн боллоо (reports/TenderForm.js, POST /TenderForm/PrintHtml ба /TenderForm/PrintReport). Маягтын толь бичгээр удирдагддаг тул шинэ маягт нэмэхэд хэвлэлт нэмэлт кодгүйгээр ажиллана. Хоосон болон бөглөсөн хувилбартай, нөхцөлт талбарыг нуух, шалгах хуудсыг Тийм/Үгүй/Тодорхойгүй нүдэн хүснэгтээр, титэм судасны 19 сегментийг нэг хүснэгтээр хэвлэнэ. Хуудасны дугаар ба эх сурвалжийн тэмдэглэгээ (байгууллага, мэдээллийн сан, огноо) хуудасны захад гарна. Батлагдсан цаасан маягттай эцсийн тулгалт ЗСҮТ-өөс эх хувь ирсний дараа (мөр 3). | 2026-09-11: Хэвлэлт маягтын хэсэг алгасах дүрмийг дагана (CAG only үед ангиопласти хэсэг хэвлэгдэхгүй, ST+ үед ST+ хэсэг хэвлэгдэнэ) — API шалгалтаар батлагдав.</t>
+  </si>
+  <si>
     <t>4. Эмчийн үзлэг</t>
   </si>
   <si>
@@ -853,7 +868,7 @@
     <t>Чухал зэрэглэлийн алдаа бүгд засагдсан</t>
   </si>
   <si>
-    <t>2026-09-10: Дотоод шалгалтаар илэрсэн 13 зөрчлийн 12-ыг зассан — Нууц үг ил хадгалагдах (User/Save), өвчтөний нууц үгийн нарийвчлалын шалгуур, файл татахад эзэмшлийн шалгалт, татгалзсан файлыг «амжилттай» гэж хариулах, байхгүй мөрийг устгахад амжилт гэж хариулах, ExportExcel хязгааргүй санах ой зарцуулах, ЭМД-ийн гадаад дуудлагад timeout байхгүй (нууц үг логт бичигдэх асуудал мөн арилав), checkConfirm-ын багана буруу бичигдсэн ба хариу буцаахгүй өлгөгдөх, Dashboard-ын 2 сервис, DoctorProfile/GetByUserId, Report/GetProvinceData, RiskScores/CalculateRisk параметр шалгахгүй унах. Үлдсэн 1: /api/base, /api/report, /api/Test токенгүй нээлттэй байгааг захиалагчийн шийдвэрээр хэвээр үлдээв (одоо байгаа дуудагчид тасалдах эрсдэлтэй тул аюулгүй байдлын аудитад шилжүүлэв). UAT хараахан эхлээгүй тул түүнээс гарах алдаа энэ мөрөнд нэмэгдэнэ.</t>
+    <t>2026-09-10: Дотоод шалгалтаар илэрсэн 13 зөрчлийн 12-ыг зассан — Нууц үг ил хадгалагдах (User/Save), өвчтөний нууц үгийн нарийвчлалын шалгуур, файл татахад эзэмшлийн шалгалт, татгалзсан файлыг «амжилттай» гэж хариулах, байхгүй мөрийг устгахад амжилт гэж хариулах, ExportExcel хязгааргүй санах ой зарцуулах, ЭМД-ийн гадаад дуудлагад timeout байхгүй (нууц үг логт бичигдэх асуудал мөн арилав), checkConfirm-ын багана буруу бичигдсэн ба хариу буцаахгүй өлгөгдөх, Dashboard-ын 2 сервис, DoctorProfile/GetByUserId, Report/GetProvinceData, RiskScores/CalculateRisk параметр шалгахгүй унах. Үлдсэн 1: /api/base, /api/report, /api/Test токенгүй нээлттэй байгааг захиалагчийн шийдвэрээр хэвээр үлдээв (одоо байгаа дуудагчид тасалдах эрсдэлтэй тул аюулгүй байдлын аудитад шилжүүлэв). UAT хараахан эхлээгүй тул түүнээс гарах алдаа энэ мөрөнд нэмэгдэнэ. | 2026-09-11: Маягтын хөдөлгүүрт 9 алдаа засав: баталгаажсан бүртгэл засагдаж болдог байсан; байгууллагын шалгалтгүй бичих; маягтын байгууллага хэзээ ч бичигддэггүй байсан (NULL); 3.1-ийн «If yes» талбарууд хэзээ ч гарахгүй байсан; 2.2-т нөхцөлт холбоос огт байгаагүй; огноо/хэмжилтүүд радио товч болж гарсан; хоосон огноонд өнөөдрийн огноо харагддаг байсан; хуулбар хуучин огноог хуулдаг байсан; шаардлагатай талбарыг сервер шалгадаггүй байсан. Гарын авлага бичих явцад илэрсэн 3 алдааг мөн засав: түгжигдсэн 1.1-1.9, 2.x маягтаас давтан мэс заслын шинэ бүртгэл үүсгэх боломжгүй байсан (одоо «Шинэ бүртгэл» товч); жагсаалтын үйлдлийн багана нарийн тул «Засах», «Устгах» дүрс харагддаггүй байсан; 3.1-ийн хэвлэлтэнд Y/N/? асуултууд тамхины сонголтын гарчиг дор хэвлэгддэг байсан. backend e5106fc, frontend 6aa138e; туршилтын орчинд шалгагдсан (8/8).</t>
   </si>
   <si>
     <t>Тестийн тайлан</t>
@@ -880,6 +895,9 @@
     <t>Гарын авлага .pdf хэлбэрээр бэлэн</t>
   </si>
   <si>
+    <t>2026-09-11: docs/handover/user-manual.md + user-manual.pdf (29 хуудас) — эмч, сувилагч, иргэний хэсгийн гарын авлага, 14 дэлгэцийн зураг (зөвхөн туршилтын өвчтөн ZZ10050154, хувийн мэдээлэлгүй). МТ-ийн утас, дэмжлэгийн холбоо барих, туршилтын ба ажлын хаягийг ЗСҮТ-ээс авч бөглөнө.</t>
+  </si>
+  <si>
     <t>Админ, суурилуулалтын гарын авлага</t>
   </si>
   <si>
@@ -889,6 +907,9 @@
     <t>Техникийн гарын авлага бэлэн</t>
   </si>
   <si>
+    <t>2026-09-11: docs/handover/admin-guide.md — суурилуулалт, тохиргоо, өгөгдлийн сан, нөөцлөлт/сэргээлт, хяналт, цагийн эх үүсвэр, аюулгүй байдал.</t>
+  </si>
+  <si>
     <t>Сервисийн баримт бичиг (API doc)</t>
   </si>
   <si>
@@ -898,7 +919,7 @@
     <t>API-ийн бүрэн баримт бичиг хүлээлгэн өгсөн</t>
   </si>
   <si>
-    <t>2026-09-10: mobile/API.md — гар утсанд хамаарах бүх сервисийн оролт, гаралт, алдааны бүрхүүл, эрхийн загварыг эх кодтой тулган баримтжуулав. Веб системийн үлдсэн 292 маршрутын баримт бичиг бичигдээгүй.</t>
+    <t>2026-09-10: mobile/API.md — гар утсанд хамаарах бүх сервисийн оролт, гаралт, алдааны бүрхүүл, эрхийн загварыг эх кодтой тулган баримтжуулав. Веб системийн үлдсэн 292 маршрутын баримт бичиг бичигдээгүй. | 2026-09-11: Веб системийн бүх үйлчилгээний цэгийн баримт бичиг: backend/docs/API-WEB.md (backend/scripts/generate_api_reference.js үүсгэнэ); гар утасны хэсэг mobile/API.md.</t>
   </si>
   <si>
     <t>Сургалтын хөтөлбөр, материал</t>
@@ -910,6 +931,9 @@
     <t>Сургалтын материал батлагдсан</t>
   </si>
   <si>
+    <t>2026-09-11: docs/handover/training.md (+слайд PDF) — сургалтын хөтөлбөр, дасгал ажил.</t>
+  </si>
+  <si>
     <t>Сургалт зохион байгуулах</t>
   </si>
   <si>
@@ -973,7 +997,7 @@
     <t>Автомат нөөцлөлт ажиллаж байна</t>
   </si>
   <si>
-    <t>2026-09-10: deploy/ хавтсанд nginx (mncardio.itsystem.mn.conf, upgrade-map), systemd (dbtunnel.service) болон 00-survey.sh тохиргоо бэлэн. Туршилтын сервер дээр pm2-logrotate суулгав (1.5 ГБ лог асуудлыг арилгав). Өгөгдлийн сангийн автомат нөөцлөлт, улсын цагийн эталон хараахан тохируулаагүй.</t>
+    <t>2026-09-10: deploy/ хавтсанд nginx (mncardio.itsystem.mn.conf, upgrade-map), systemd (dbtunnel.service) болон 00-survey.sh тохиргоо бэлэн. Туршилтын сервер дээр pm2-logrotate суулгав (1.5 ГБ лог асуудлыг арилгав). Өгөгдлийн сангийн автомат нөөцлөлт, улсын цагийн эталон хараахан тохируулаагүй. | 2026-09-11: backend/scripts/spFullBackup.sql бичигдэв (ажиллуулаагүй — DBA хянаж үүсгэнэ); нөөцлөлт, сэргээлтийн заавар docs/handover/admin-guide.md-д.</t>
   </si>
   <si>
     <t>Хүлээлцэх акт</t>
@@ -5937,7 +5961,9 @@
       <c r="K29" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L29" s="19"/>
+      <c r="L29" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
@@ -5953,7 +5979,7 @@
         <v>140</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>16</v>
@@ -5971,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L30" s="19"/>
     </row>
@@ -5989,7 +6015,7 @@
         <v>140</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>16</v>
@@ -6007,10 +6033,10 @@
         <v>1</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L31" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6027,7 +6053,7 @@
         <v>140</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>17</v>
@@ -6045,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L32" s="19"/>
     </row>
@@ -6060,7 +6086,7 @@
         <v>139</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>141</v>
@@ -6098,7 +6124,7 @@
         <v>139</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>144</v>
@@ -6134,7 +6160,7 @@
         <v>139</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>146</v>
@@ -6157,7 +6183,9 @@
       <c r="K35" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L35" s="19"/>
+      <c r="L35" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
@@ -6170,10 +6198,10 @@
         <v>139</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>16</v>
@@ -6191,7 +6219,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L36" s="19"/>
     </row>
@@ -6206,10 +6234,10 @@
         <v>139</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>16</v>
@@ -6227,10 +6255,10 @@
         <v>1</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L37" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6244,10 +6272,10 @@
         <v>139</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>17</v>
@@ -6265,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L38" s="19"/>
     </row>
@@ -6280,7 +6308,7 @@
         <v>139</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>141</v>
@@ -6318,7 +6346,7 @@
         <v>139</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>144</v>
@@ -6354,7 +6382,7 @@
         <v>139</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>146</v>
@@ -6377,7 +6405,9 @@
       <c r="K41" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L41" s="19"/>
+      <c r="L41" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
@@ -6390,10 +6420,10 @@
         <v>139</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>16</v>
@@ -6411,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L42" s="19"/>
     </row>
@@ -6426,10 +6456,10 @@
         <v>139</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>16</v>
@@ -6447,10 +6477,10 @@
         <v>0.5</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6464,10 +6494,10 @@
         <v>139</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>17</v>
@@ -6485,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L44" s="19"/>
     </row>
@@ -6500,7 +6530,7 @@
         <v>139</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>141</v>
@@ -6524,7 +6554,7 @@
         <v>142</v>
       </c>
       <c r="L45" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6538,7 +6568,7 @@
         <v>139</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>144</v>
@@ -6562,7 +6592,7 @@
         <v>145</v>
       </c>
       <c r="L46" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6576,10 +6606,10 @@
         <v>139</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>16</v>
@@ -6597,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6614,7 +6644,7 @@
         <v>139</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>141</v>
@@ -6638,7 +6668,7 @@
         <v>142</v>
       </c>
       <c r="L48" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6652,7 +6682,7 @@
         <v>139</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>144</v>
@@ -6688,7 +6718,7 @@
         <v>139</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>146</v>
@@ -6711,7 +6741,9 @@
       <c r="K50" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L50" s="19"/>
+      <c r="L50" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
@@ -6724,10 +6756,10 @@
         <v>139</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>16</v>
@@ -6745,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L51" s="19"/>
     </row>
@@ -6760,10 +6792,10 @@
         <v>139</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>16</v>
@@ -6781,10 +6813,10 @@
         <v>0.5</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L52" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6798,10 +6830,10 @@
         <v>139</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>17</v>
@@ -6819,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L53" s="19"/>
     </row>
@@ -6834,7 +6866,7 @@
         <v>139</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>141</v>
@@ -6858,7 +6890,7 @@
         <v>142</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6872,7 +6904,7 @@
         <v>139</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>144</v>
@@ -6908,7 +6940,7 @@
         <v>139</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>146</v>
@@ -6931,7 +6963,9 @@
       <c r="K56" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L56" s="19"/>
+      <c r="L56" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="17">
@@ -6944,10 +6978,10 @@
         <v>139</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>16</v>
@@ -6965,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L57" s="19"/>
     </row>
@@ -6980,10 +7014,10 @@
         <v>139</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>16</v>
@@ -7001,10 +7035,10 @@
         <v>0.5</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7018,10 +7052,10 @@
         <v>139</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>17</v>
@@ -7039,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L59" s="19"/>
     </row>
@@ -7054,7 +7088,7 @@
         <v>139</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>141</v>
@@ -7078,7 +7112,7 @@
         <v>142</v>
       </c>
       <c r="L60" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7092,7 +7126,7 @@
         <v>139</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>144</v>
@@ -7128,7 +7162,7 @@
         <v>139</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>146</v>
@@ -7151,7 +7185,9 @@
       <c r="K62" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L62" s="19"/>
+      <c r="L62" s="19" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="17">
@@ -7164,10 +7200,10 @@
         <v>139</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>16</v>
@@ -7185,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L63" s="19"/>
     </row>
@@ -7200,10 +7236,10 @@
         <v>139</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>16</v>
@@ -7221,10 +7257,10 @@
         <v>0.5</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L64" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7238,10 +7274,10 @@
         <v>139</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>17</v>
@@ -7259,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L65" s="19"/>
     </row>
@@ -7274,7 +7310,7 @@
         <v>139</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E66" s="19" t="s">
         <v>141</v>
@@ -7298,7 +7334,7 @@
         <v>142</v>
       </c>
       <c r="L66" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7312,7 +7348,7 @@
         <v>139</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E67" s="19" t="s">
         <v>144</v>
@@ -7348,7 +7384,7 @@
         <v>139</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E68" s="19" t="s">
         <v>146</v>
@@ -7371,7 +7407,9 @@
       <c r="K68" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L68" s="19"/>
+      <c r="L68" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="17">
@@ -7384,10 +7422,10 @@
         <v>139</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>16</v>
@@ -7405,7 +7443,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L69" s="19"/>
     </row>
@@ -7420,10 +7458,10 @@
         <v>139</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>16</v>
@@ -7441,10 +7479,10 @@
         <v>0.5</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L70" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7458,10 +7496,10 @@
         <v>139</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>17</v>
@@ -7479,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L71" s="19"/>
     </row>
@@ -7494,7 +7532,7 @@
         <v>139</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>141</v>
@@ -7518,7 +7556,7 @@
         <v>142</v>
       </c>
       <c r="L72" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7532,7 +7570,7 @@
         <v>139</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>144</v>
@@ -7568,7 +7606,7 @@
         <v>139</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>146</v>
@@ -7591,7 +7629,9 @@
       <c r="K74" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L74" s="19"/>
+      <c r="L74" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="17">
@@ -7604,10 +7644,10 @@
         <v>139</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>16</v>
@@ -7625,7 +7665,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L75" s="19"/>
     </row>
@@ -7640,10 +7680,10 @@
         <v>139</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>16</v>
@@ -7661,10 +7701,10 @@
         <v>1</v>
       </c>
       <c r="K76" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L76" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7678,10 +7718,10 @@
         <v>139</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>17</v>
@@ -7699,7 +7739,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L77" s="19"/>
     </row>
@@ -7714,7 +7754,7 @@
         <v>139</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>141</v>
@@ -7738,7 +7778,7 @@
         <v>142</v>
       </c>
       <c r="L78" s="19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7752,7 +7792,7 @@
         <v>139</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>144</v>
@@ -7776,7 +7816,7 @@
         <v>145</v>
       </c>
       <c r="L79" s="19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7790,10 +7830,10 @@
         <v>139</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>16</v>
@@ -7811,10 +7851,10 @@
         <v>1</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L80" s="19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7825,10 +7865,10 @@
         <v>28</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>141</v>
@@ -7852,7 +7892,7 @@
         <v>142</v>
       </c>
       <c r="L81" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7863,10 +7903,10 @@
         <v>28</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>144</v>
@@ -7899,10 +7939,10 @@
         <v>28</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>146</v>
@@ -7925,7 +7965,9 @@
       <c r="K83" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L83" s="19"/>
+      <c r="L83" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="17">
@@ -7935,13 +7977,13 @@
         <v>28</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>16</v>
@@ -7959,7 +8001,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L84" s="19"/>
     </row>
@@ -7971,13 +8013,13 @@
         <v>28</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>16</v>
@@ -7995,10 +8037,10 @@
         <v>1</v>
       </c>
       <c r="K85" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L85" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8009,13 +8051,13 @@
         <v>28</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>17</v>
@@ -8033,7 +8075,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L86" s="19"/>
     </row>
@@ -8045,10 +8087,10 @@
         <v>28</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>141</v>
@@ -8072,7 +8114,7 @@
         <v>142</v>
       </c>
       <c r="L87" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8083,10 +8125,10 @@
         <v>28</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>144</v>
@@ -8110,7 +8152,7 @@
         <v>145</v>
       </c>
       <c r="L88" s="19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8121,10 +8163,10 @@
         <v>28</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>146</v>
@@ -8148,7 +8190,7 @@
         <v>147</v>
       </c>
       <c r="L89" s="19" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8159,13 +8201,13 @@
         <v>28</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F90" s="17" t="s">
         <v>16</v>
@@ -8183,10 +8225,10 @@
         <v>1</v>
       </c>
       <c r="K90" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L90" s="19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8197,13 +8239,13 @@
         <v>28</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F91" s="17" t="s">
         <v>16</v>
@@ -8221,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="K91" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8235,13 +8277,13 @@
         <v>28</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F92" s="17" t="s">
         <v>17</v>
@@ -8259,10 +8301,10 @@
         <v>0</v>
       </c>
       <c r="K92" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L92" s="19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8273,10 +8315,10 @@
         <v>28</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E93" s="19" t="s">
         <v>141</v>
@@ -8300,7 +8342,7 @@
         <v>142</v>
       </c>
       <c r="L93" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8311,10 +8353,10 @@
         <v>28</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>144</v>
@@ -8347,10 +8389,10 @@
         <v>28</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E95" s="19" t="s">
         <v>146</v>
@@ -8373,7 +8415,9 @@
       <c r="K95" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L95" s="19"/>
+      <c r="L95" s="19" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="96" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="17">
@@ -8383,13 +8427,13 @@
         <v>28</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F96" s="17" t="s">
         <v>16</v>
@@ -8407,10 +8451,10 @@
         <v>1</v>
       </c>
       <c r="K96" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L96" s="19" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8421,13 +8465,13 @@
         <v>28</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F97" s="17" t="s">
         <v>16</v>
@@ -8445,10 +8489,10 @@
         <v>1</v>
       </c>
       <c r="K97" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L97" s="19" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8459,13 +8503,13 @@
         <v>28</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F98" s="17" t="s">
         <v>17</v>
@@ -8483,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L98" s="19"/>
     </row>
@@ -8495,10 +8539,10 @@
         <v>28</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>141</v>
@@ -8522,7 +8566,7 @@
         <v>142</v>
       </c>
       <c r="L99" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8533,10 +8577,10 @@
         <v>28</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>144</v>
@@ -8569,10 +8613,10 @@
         <v>28</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>146</v>
@@ -8605,13 +8649,13 @@
         <v>28</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F102" s="17" t="s">
         <v>16</v>
@@ -8629,10 +8673,10 @@
         <v>1</v>
       </c>
       <c r="K102" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L102" s="19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8643,13 +8687,13 @@
         <v>28</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F103" s="17" t="s">
         <v>16</v>
@@ -8667,10 +8711,10 @@
         <v>1</v>
       </c>
       <c r="K103" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L103" s="19" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8681,13 +8725,13 @@
         <v>28</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F104" s="17" t="s">
         <v>17</v>
@@ -8705,7 +8749,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L104" s="19"/>
     </row>
@@ -8717,13 +8761,13 @@
         <v>28</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F105" s="17" t="s">
         <v>16</v>
@@ -8741,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="K105" s="19" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L105" s="19"/>
     </row>
@@ -8753,13 +8797,13 @@
         <v>28</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F106" s="17" t="s">
         <v>16</v>
@@ -8777,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="K106" s="19" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L106" s="19"/>
     </row>
@@ -8789,13 +8833,13 @@
         <v>28</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F107" s="17" t="s">
         <v>16</v>
@@ -8813,10 +8857,10 @@
         <v>1</v>
       </c>
       <c r="K107" s="19" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L107" s="19" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8827,13 +8871,13 @@
         <v>28</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F108" s="17" t="s">
         <v>16</v>
@@ -8851,10 +8895,10 @@
         <v>1</v>
       </c>
       <c r="K108" s="19" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L108" s="19" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8865,13 +8909,13 @@
         <v>28</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F109" s="17" t="s">
         <v>17</v>
@@ -8889,10 +8933,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="19" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L109" s="19" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8903,13 +8947,13 @@
         <v>28</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F110" s="17" t="s">
         <v>16</v>
@@ -8927,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="19" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L110" s="19" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8941,13 +8985,13 @@
         <v>28</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F111" s="17" t="s">
         <v>16</v>
@@ -8965,10 +9009,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="19" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="L111" s="19" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8979,13 +9023,13 @@
         <v>28</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F112" s="17" t="s">
         <v>17</v>
@@ -9003,10 +9047,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="L112" s="19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9017,13 +9061,13 @@
         <v>28</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F113" s="17" t="s">
         <v>16</v>
@@ -9041,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L113" s="19" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9055,13 +9099,13 @@
         <v>28</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F114" s="17" t="s">
         <v>16</v>
@@ -9079,10 +9123,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L114" s="19" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9093,13 +9137,13 @@
         <v>28</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F115" s="17" t="s">
         <v>17</v>
@@ -9117,10 +9161,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="L115" s="19" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9131,13 +9175,13 @@
         <v>28</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F116" s="17" t="s">
         <v>16</v>
@@ -9155,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L116" s="19"/>
     </row>
@@ -9167,13 +9211,13 @@
         <v>28</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F117" s="17" t="s">
         <v>16</v>
@@ -9191,7 +9235,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L117" s="19"/>
     </row>
@@ -9203,13 +9247,13 @@
         <v>28</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F118" s="17" t="s">
         <v>17</v>
@@ -9227,10 +9271,10 @@
         <v>0</v>
       </c>
       <c r="K118" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="L118" s="19" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9241,13 +9285,13 @@
         <v>28</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F119" s="17" t="s">
         <v>16</v>
@@ -9265,10 +9309,10 @@
         <v>0</v>
       </c>
       <c r="K119" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L119" s="19" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9279,13 +9323,13 @@
         <v>28</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F120" s="17" t="s">
         <v>16</v>
@@ -9303,10 +9347,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L120" s="19" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9317,13 +9361,13 @@
         <v>28</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F121" s="17" t="s">
         <v>17</v>
@@ -9341,10 +9385,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="L121" s="19" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9355,13 +9399,13 @@
         <v>28</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F122" s="17" t="s">
         <v>16</v>
@@ -9379,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L122" s="19"/>
     </row>
@@ -9391,13 +9435,13 @@
         <v>28</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F123" s="17" t="s">
         <v>16</v>
@@ -9415,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L123" s="19"/>
     </row>
@@ -9427,13 +9471,13 @@
         <v>28</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F124" s="17" t="s">
         <v>17</v>
@@ -9451,10 +9495,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="L124" s="19" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9465,13 +9509,13 @@
         <v>28</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F125" s="17" t="s">
         <v>16</v>
@@ -9489,7 +9533,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L125" s="19"/>
     </row>
@@ -9501,13 +9545,13 @@
         <v>28</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D126" s="19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F126" s="17" t="s">
         <v>16</v>
@@ -9525,7 +9569,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L126" s="19"/>
     </row>
@@ -9537,13 +9581,13 @@
         <v>28</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F127" s="17" t="s">
         <v>17</v>
@@ -9561,10 +9605,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="L127" s="19" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9575,13 +9619,13 @@
         <v>28</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D128" s="19" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F128" s="17" t="s">
         <v>16</v>
@@ -9599,7 +9643,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L128" s="19"/>
     </row>
@@ -9611,13 +9655,13 @@
         <v>28</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>16</v>
@@ -9635,7 +9679,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L129" s="19"/>
     </row>
@@ -9647,13 +9691,13 @@
         <v>28</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D130" s="19" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E130" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F130" s="17" t="s">
         <v>17</v>
@@ -9671,10 +9715,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="L130" s="19" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9685,13 +9729,13 @@
         <v>28</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D131" s="19" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F131" s="17" t="s">
         <v>16</v>
@@ -9709,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L131" s="19"/>
     </row>
@@ -9721,13 +9765,13 @@
         <v>28</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F132" s="17" t="s">
         <v>16</v>
@@ -9745,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L132" s="19"/>
     </row>
@@ -9757,13 +9801,13 @@
         <v>28</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>16</v>
@@ -9781,10 +9825,10 @@
         <v>1</v>
       </c>
       <c r="K133" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L133" s="19" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9795,13 +9839,13 @@
         <v>28</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D134" s="19" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E134" s="19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F134" s="17" t="s">
         <v>16</v>
@@ -9819,10 +9863,10 @@
         <v>0.5</v>
       </c>
       <c r="K134" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L134" s="19" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9833,13 +9877,13 @@
         <v>30</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F135" s="17" t="s">
         <v>16</v>
@@ -9857,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="19" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="L135" s="19"/>
     </row>
@@ -9869,13 +9913,13 @@
         <v>30</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F136" s="17" t="s">
         <v>16</v>
@@ -9893,10 +9937,10 @@
         <v>0.7</v>
       </c>
       <c r="K136" s="19" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L136" s="19" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9907,13 +9951,13 @@
         <v>30</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D137" s="19" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E137" s="19" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F137" s="17" t="s">
         <v>16</v>
@@ -9931,10 +9975,10 @@
         <v>0.3</v>
       </c>
       <c r="K137" s="19" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="L137" s="19" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" ht="15.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9945,13 +9989,13 @@
         <v>30</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D138" s="19" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E138" s="19" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F138" s="17" t="s">
         <v>17</v>
@@ -9969,10 +10013,10 @@
         <v>0</v>
       </c>
       <c r="K138" s="19" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="L138" s="19" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="139" ht="15.6" customHeight="1" hidden="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9983,13 +10027,13 @@
         <v>30</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D139" s="19" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E139" s="19" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F139" s="17" t="s">
         <v>17</v>
@@ -10007,10 +10051,10 @@
         <v>0</v>
       </c>
       <c r="K139" s="19" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="L139" s="19" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10021,13 +10065,13 @@
         <v>30</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D140" s="19" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F140" s="17" t="s">
         <v>16</v>
@@ -10045,10 +10089,10 @@
         <v>0</v>
       </c>
       <c r="K140" s="19" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L140" s="19" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10059,13 +10103,13 @@
         <v>30</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D141" s="19" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E141" s="19" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F141" s="17" t="s">
         <v>17</v>
@@ -10083,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="19" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="L141" s="19"/>
     </row>
@@ -10095,13 +10139,13 @@
         <v>30</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D142" s="19" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E142" s="19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F142" s="17" t="s">
         <v>16</v>
@@ -10119,10 +10163,10 @@
         <v>0.4</v>
       </c>
       <c r="K142" s="19" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="L142" s="19" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10133,13 +10177,13 @@
         <v>30</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D143" s="19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E143" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F143" s="17" t="s">
         <v>16</v>
@@ -10157,10 +10201,10 @@
         <v>0.3</v>
       </c>
       <c r="K143" s="19" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L143" s="19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10171,13 +10215,13 @@
         <v>32</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E144" s="19" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F144" s="17" t="s">
         <v>16</v>
@@ -10189,15 +10233,17 @@
         <v>46267</v>
       </c>
       <c r="I144" s="17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J144" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K144" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="L144" s="19"/>
+        <v>290</v>
+      </c>
+      <c r="L144" s="19" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="145" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="17">
@@ -10207,13 +10253,13 @@
         <v>32</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D145" s="19" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E145" s="19" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F145" s="17" t="s">
         <v>16</v>
@@ -10225,15 +10271,17 @@
         <v>46267</v>
       </c>
       <c r="I145" s="17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J145" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="L145" s="19"/>
+        <v>294</v>
+      </c>
+      <c r="L145" s="19" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="146" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="17">
@@ -10243,13 +10291,13 @@
         <v>32</v>
       </c>
       <c r="C146" s="19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E146" s="19" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="F146" s="17" t="s">
         <v>16</v>
@@ -10261,16 +10309,16 @@
         <v>46268</v>
       </c>
       <c r="I146" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J146" s="23">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K146" s="19" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="L146" s="19" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10281,13 +10329,13 @@
         <v>32</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D147" s="19" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E147" s="19" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F147" s="17" t="s">
         <v>16</v>
@@ -10299,15 +10347,17 @@
         <v>46266</v>
       </c>
       <c r="I147" s="17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J147" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="L147" s="19"/>
+        <v>302</v>
+      </c>
+      <c r="L147" s="19" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="148" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="17">
@@ -10317,13 +10367,13 @@
         <v>32</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D148" s="19" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E148" s="19" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F148" s="17" t="s">
         <v>17</v>
@@ -10341,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="19" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="L148" s="19"/>
     </row>
@@ -10353,13 +10403,13 @@
         <v>32</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D149" s="19" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E149" s="19" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F149" s="17" t="s">
         <v>16</v>
@@ -10377,7 +10427,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="19" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="L149" s="19"/>
     </row>
@@ -10389,13 +10439,13 @@
         <v>34</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D150" s="19" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E150" s="19" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F150" s="17" t="s">
         <v>16</v>
@@ -10413,10 +10463,10 @@
         <v>0.4</v>
       </c>
       <c r="K150" s="19" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L150" s="19" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10427,13 +10477,13 @@
         <v>34</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D151" s="19" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F151" s="17" t="s">
         <v>16</v>
@@ -10451,10 +10501,10 @@
         <v>0.4</v>
       </c>
       <c r="K151" s="19" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="L151" s="19" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10465,13 +10515,13 @@
         <v>34</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D152" s="19" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E152" s="19" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F152" s="17" t="s">
         <v>17</v>
@@ -10489,7 +10539,7 @@
         <v>0</v>
       </c>
       <c r="K152" s="19" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="L152" s="19"/>
     </row>
@@ -10501,13 +10551,13 @@
         <v>34</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D153" s="19" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E153" s="19" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F153" s="17" t="s">
         <v>16</v>
@@ -10525,10 +10575,10 @@
         <v>0.4</v>
       </c>
       <c r="K153" s="19" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="L153" s="19" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10539,13 +10589,13 @@
         <v>34</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D154" s="19" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E154" s="19" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F154" s="17" t="s">
         <v>17</v>
@@ -10563,7 +10613,7 @@
         <v>0</v>
       </c>
       <c r="K154" s="19" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="L154" s="19"/>
     </row>
@@ -10575,13 +10625,13 @@
         <v>36</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D155" s="19" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E155" s="19" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F155" s="17" t="s">
         <v>16</v>
@@ -10599,7 +10649,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="19" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="L155" s="19"/>
     </row>
@@ -10611,13 +10661,13 @@
         <v>36</v>
       </c>
       <c r="C156" s="19" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D156" s="19" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E156" s="19" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F156" s="17" t="s">
         <v>16</v>
@@ -10635,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="K156" s="19" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="L156" s="19"/>
     </row>
@@ -10647,13 +10697,13 @@
         <v>36</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D157" s="19" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E157" s="19" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F157" s="17" t="s">
         <v>17</v>
@@ -10671,853 +10721,853 @@
         <v>0</v>
       </c>
       <c r="K157" s="19" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="L157" s="19"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A4:L157"/>
   <conditionalFormatting sqref="H5:H157">
@@ -11640,13 +11690,13 @@
         <v>39</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>16</v>
@@ -11664,10 +11714,10 @@
         <v>1</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11678,13 +11728,13 @@
         <v>39</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>16</v>
@@ -11702,10 +11752,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11716,13 +11766,13 @@
         <v>39</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>16</v>
@@ -11740,10 +11790,10 @@
         <v>1</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11754,13 +11804,13 @@
         <v>39</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>17</v>
@@ -11778,7 +11828,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L8" s="19" t="s">
         <v>101</v>
@@ -11792,13 +11842,13 @@
         <v>39</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>16</v>
@@ -11816,10 +11866,10 @@
         <v>1</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11830,13 +11880,13 @@
         <v>39</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>17</v>
@@ -11854,10 +11904,10 @@
         <v>1</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11868,13 +11918,13 @@
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>16</v>
@@ -11892,10 +11942,10 @@
         <v>1</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11906,13 +11956,13 @@
         <v>41</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>16</v>
@@ -11930,10 +11980,10 @@
         <v>1</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11944,13 +11994,13 @@
         <v>41</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>16</v>
@@ -11968,10 +12018,10 @@
         <v>1</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11982,13 +12032,13 @@
         <v>41</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>16</v>
@@ -12006,10 +12056,10 @@
         <v>1</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="L14" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12020,13 +12070,13 @@
         <v>41</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>17</v>
@@ -12044,10 +12094,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="L15" s="19" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12058,13 +12108,13 @@
         <v>43</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>16</v>
@@ -12082,10 +12132,10 @@
         <v>1</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" ht="39.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12096,13 +12146,13 @@
         <v>43</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>16</v>
@@ -12120,10 +12170,10 @@
         <v>1</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" ht="66" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12134,13 +12184,13 @@
         <v>43</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>16</v>
@@ -12158,10 +12208,10 @@
         <v>0</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" ht="79.2" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12172,13 +12222,13 @@
         <v>43</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>16</v>
@@ -12196,10 +12246,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="L19" s="19" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -12210,13 +12260,13 @@
         <v>43</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>16</v>
@@ -12234,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="L20" s="19"/>
     </row>
@@ -12246,13 +12296,13 @@
         <v>43</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>16</v>
@@ -12270,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="L21" s="19"/>
     </row>
@@ -12282,13 +12332,13 @@
         <v>43</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>16</v>
@@ -12306,7 +12356,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="L22" s="19"/>
     </row>
@@ -12318,13 +12368,13 @@
         <v>43</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>16</v>
@@ -12342,7 +12392,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="L23" s="19"/>
     </row>
@@ -12354,13 +12404,13 @@
         <v>43</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>16</v>
@@ -12378,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="L24" s="19"/>
     </row>
@@ -12390,13 +12440,13 @@
         <v>43</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>16</v>
@@ -12414,7 +12464,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="L25" s="19"/>
     </row>
@@ -12426,13 +12476,13 @@
         <v>43</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>17</v>
@@ -12450,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="L26" s="19" t="s">
         <v>94</v>
@@ -12464,13 +12514,13 @@
         <v>43</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>16</v>
@@ -12488,7 +12538,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="L27" s="19"/>
     </row>
@@ -12500,13 +12550,13 @@
         <v>43</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>16</v>
@@ -12524,10 +12574,10 @@
         <v>0</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12538,13 +12588,13 @@
         <v>43</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>16</v>
@@ -12562,7 +12612,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="L29" s="19"/>
     </row>
@@ -12574,13 +12624,13 @@
         <v>43</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>16</v>
@@ -12598,7 +12648,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="L30" s="19"/>
     </row>
@@ -12610,13 +12660,13 @@
         <v>43</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>16</v>
@@ -12634,7 +12684,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="L31" s="19"/>
     </row>
@@ -12646,13 +12696,13 @@
         <v>45</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>16</v>
@@ -12670,10 +12720,10 @@
         <v>0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="L32" s="19" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12684,13 +12734,13 @@
         <v>45</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>16</v>
@@ -12708,10 +12758,10 @@
         <v>0</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="L33" s="19" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12722,13 +12772,13 @@
         <v>45</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>16</v>
@@ -12746,10 +12796,10 @@
         <v>0</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12760,13 +12810,13 @@
         <v>45</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>16</v>
@@ -12784,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="L35" s="19" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12798,13 +12848,13 @@
         <v>45</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>16</v>
@@ -12822,10 +12872,10 @@
         <v>0</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="L36" s="19" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12836,13 +12886,13 @@
         <v>45</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>17</v>
@@ -12860,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="L37" s="19"/>
     </row>
@@ -12872,13 +12922,13 @@
         <v>47</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>16</v>
@@ -12896,10 +12946,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="19" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="L38" s="19" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12910,13 +12960,13 @@
         <v>47</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>16</v>
@@ -12934,10 +12984,10 @@
         <v>0</v>
       </c>
       <c r="K39" s="19" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="L39" s="19" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12948,13 +12998,13 @@
         <v>47</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>16</v>
@@ -12972,10 +13022,10 @@
         <v>0</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="L40" s="19" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -12986,13 +13036,13 @@
         <v>47</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>16</v>
@@ -13010,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="19" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L41" s="19" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13024,13 +13074,13 @@
         <v>47</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>17</v>
@@ -13048,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="L42" s="19" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13062,13 +13112,13 @@
         <v>47</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>16</v>
@@ -13086,10 +13136,10 @@
         <v>0</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13100,13 +13150,13 @@
         <v>47</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>16</v>
@@ -13124,10 +13174,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="19" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="L44" s="19" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13138,13 +13188,13 @@
         <v>47</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>16</v>
@@ -13162,10 +13212,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="19" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="L45" s="19" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13176,13 +13226,13 @@
         <v>49</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>16</v>
@@ -13200,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="19" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="L46" s="19"/>
     </row>
@@ -13212,13 +13262,13 @@
         <v>49</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>16</v>
@@ -13236,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="L47" s="19"/>
     </row>
@@ -13248,13 +13298,13 @@
         <v>49</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>16</v>
@@ -13272,7 +13322,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="L48" s="19"/>
     </row>
@@ -13284,13 +13334,13 @@
         <v>49</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>16</v>
@@ -13308,7 +13358,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="19" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="L49" s="19"/>
     </row>
@@ -13320,13 +13370,13 @@
         <v>49</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>16</v>
@@ -13344,7 +13394,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="L50" s="19"/>
     </row>
@@ -13356,13 +13406,13 @@
         <v>49</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>16</v>
@@ -13380,7 +13430,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="L51" s="19"/>
     </row>
@@ -13392,13 +13442,13 @@
         <v>49</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>16</v>
@@ -13416,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="L52" s="19"/>
     </row>
@@ -13428,13 +13478,13 @@
         <v>49</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>16</v>
@@ -13452,7 +13502,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="L53" s="19"/>
     </row>
@@ -13464,13 +13514,13 @@
         <v>49</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>16</v>
@@ -13488,10 +13538,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13502,13 +13552,13 @@
         <v>49</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>16</v>
@@ -13526,10 +13576,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="L55" s="19" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13540,13 +13590,13 @@
         <v>49</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>16</v>
@@ -13564,7 +13614,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="L56" s="19"/>
     </row>
@@ -13576,13 +13626,13 @@
         <v>49</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>16</v>
@@ -13600,10 +13650,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13614,13 +13664,13 @@
         <v>49</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>17</v>
@@ -13638,10 +13688,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13652,13 +13702,13 @@
         <v>49</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>16</v>
@@ -13676,10 +13726,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13690,13 +13740,13 @@
         <v>49</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>16</v>
@@ -13714,10 +13764,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="19" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="L60" s="19" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13728,13 +13778,13 @@
         <v>51</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>16</v>
@@ -13752,7 +13802,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="L61" s="19"/>
     </row>
@@ -13764,13 +13814,13 @@
         <v>51</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>16</v>
@@ -13788,7 +13838,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="L62" s="19"/>
     </row>
@@ -13800,13 +13850,13 @@
         <v>51</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>17</v>
@@ -13824,7 +13874,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="19" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="L63" s="19"/>
     </row>
@@ -13836,13 +13886,13 @@
         <v>51</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>16</v>
@@ -13860,7 +13910,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="L64" s="19"/>
     </row>
@@ -13872,13 +13922,13 @@
         <v>51</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>16</v>
@@ -13896,7 +13946,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="L65" s="19"/>
     </row>
@@ -13908,13 +13958,13 @@
         <v>51</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>16</v>
@@ -13932,7 +13982,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="L66" s="19"/>
     </row>
@@ -13944,13 +13994,13 @@
         <v>51</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>16</v>
@@ -13968,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="19" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="L67" s="19"/>
     </row>
@@ -13980,13 +14030,13 @@
         <v>51</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>16</v>
@@ -14004,7 +14054,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="19" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="L68" s="19"/>
     </row>
@@ -14016,13 +14066,13 @@
         <v>53</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>16</v>
@@ -14040,7 +14090,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="19" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="L69" s="19"/>
     </row>
@@ -14052,13 +14102,13 @@
         <v>53</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>16</v>
@@ -14076,7 +14126,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="L70" s="19"/>
     </row>
@@ -14088,13 +14138,13 @@
         <v>53</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>17</v>
@@ -14112,7 +14162,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="19" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="L71" s="19"/>
     </row>
@@ -14124,13 +14174,13 @@
         <v>53</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F72" s="17" t="s">
         <v>17</v>
@@ -14148,7 +14198,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="19" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L72" s="19"/>
     </row>
@@ -14160,13 +14210,13 @@
         <v>53</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>17</v>
@@ -14184,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="19" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="L73" s="19"/>
     </row>
@@ -14196,13 +14246,13 @@
         <v>53</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>16</v>
@@ -14220,7 +14270,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="L74" s="19"/>
     </row>
@@ -14232,13 +14282,13 @@
         <v>55</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>17</v>
@@ -14256,7 +14306,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="19" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="L75" s="19"/>
     </row>
@@ -14268,13 +14318,13 @@
         <v>55</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>16</v>
@@ -14292,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="19" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="L76" s="19"/>
     </row>
@@ -14304,13 +14354,13 @@
         <v>55</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>16</v>
@@ -14328,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="19" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="L77" s="19"/>
     </row>
@@ -14340,13 +14390,13 @@
         <v>55</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>16</v>
@@ -14364,7 +14414,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="19" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L78" s="19"/>
     </row>
@@ -14376,13 +14426,13 @@
         <v>55</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>16</v>
@@ -14400,7 +14450,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="19" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="L79" s="19"/>
     </row>
@@ -14412,13 +14462,13 @@
         <v>57</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>16</v>
@@ -14436,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L80" s="19"/>
     </row>
@@ -14448,13 +14498,13 @@
         <v>57</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="F81" s="17" t="s">
         <v>16</v>
@@ -14472,7 +14522,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="19" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="L81" s="19"/>
     </row>
@@ -14484,13 +14534,13 @@
         <v>57</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="F82" s="17" t="s">
         <v>16</v>
@@ -14508,7 +14558,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="19" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="L82" s="19"/>
     </row>
@@ -14520,13 +14570,13 @@
         <v>57</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="F83" s="17" t="s">
         <v>17</v>
@@ -14544,7 +14594,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="19" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="L83" s="19"/>
     </row>
@@ -14556,13 +14606,13 @@
         <v>57</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>17</v>
@@ -14580,7 +14630,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="19" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="L84" s="19"/>
     </row>
@@ -14592,13 +14642,13 @@
         <v>57</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>16</v>
@@ -14616,7 +14666,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="19" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="L85" s="19"/>
     </row>
@@ -14628,13 +14678,13 @@
         <v>57</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>17</v>
@@ -14652,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="19" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="L86" s="19"/>
     </row>
@@ -15638,17 +15688,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15657,33 +15707,33 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -15699,28 +15749,28 @@
         <v>1</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15728,28 +15778,28 @@
         <v>2</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15757,28 +15807,28 @@
         <v>3</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="E9" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>626</v>
       </c>
-      <c r="F9" s="26" t="s">
-        <v>618</v>
-      </c>
       <c r="G9" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15786,28 +15836,28 @@
         <v>4</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>636</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>637</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>626</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>627</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>628</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>629</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>630</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>618</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>618</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>619</v>
-      </c>
       <c r="I10" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15815,28 +15865,28 @@
         <v>5</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="12" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15844,28 +15894,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="13" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15873,28 +15923,28 @@
         <v>7</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="14" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15902,28 +15952,28 @@
         <v>8</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15931,28 +15981,28 @@
         <v>9</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="16" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15960,28 +16010,28 @@
         <v>10</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="17" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15989,28 +16039,28 @@
         <v>11</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I17" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="18" ht="396.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16018,28 +16068,28 @@
         <v>12</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" ht="396.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16047,28 +16097,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="20" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16076,28 +16126,28 @@
         <v>14</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="21" ht="85.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16105,28 +16155,28 @@
         <v>15</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="22" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16134,28 +16184,28 @@
         <v>16</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="23" ht="111.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16163,28 +16213,28 @@
         <v>17</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="24" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16192,34 +16242,34 @@
         <v>18</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="25" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -16235,28 +16285,28 @@
         <v>19</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16264,28 +16314,28 @@
         <v>20</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="29" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16293,28 +16343,28 @@
         <v>21</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="30" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16322,28 +16372,28 @@
         <v>22</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="31" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16351,28 +16401,28 @@
         <v>23</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I31" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="32" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16380,28 +16430,28 @@
         <v>24</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16409,28 +16459,28 @@
         <v>25</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="34" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16438,28 +16488,28 @@
         <v>26</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="35" ht="111.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16467,28 +16517,28 @@
         <v>27</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="36" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16496,28 +16546,28 @@
         <v>28</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="37" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16525,28 +16575,28 @@
         <v>29</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16554,28 +16604,28 @@
         <v>30</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="39" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16583,28 +16633,28 @@
         <v>31</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="40" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16612,28 +16662,28 @@
         <v>32</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="41" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16641,28 +16691,28 @@
         <v>33</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="42" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16670,34 +16720,34 @@
         <v>34</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="43" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
@@ -16725,7 +16775,7 @@
     <hyperlink ref="E20" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId8"/>
 </worksheet>
 </file>
--- a/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
+++ b/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="749">
   <si>
     <t>ХЯНАЛТЫН САМБАР</t>
   </si>
@@ -772,10 +772,10 @@
     <t>Гар утасны аппликэйшнд зориулсан API нээх — хөгжүүлэлт, тохиргоо</t>
   </si>
   <si>
-    <t>2026-09-10: Гар утасны API нээгдэв — /api/doctor (12 маршрут: /me, /visits, /monitoring, /advice, /reports/summary, /patients) ба /api/patient (16 маршрут: /me, /journal, /questions, /advice, /risk, /evisits, /rehab/*), server.js:373-382. Бодит HTTP төлөвийн код, жижиг үсгийн {success,message,data} бүрхүүлтэй. Гэрээний бүрэн тодорхойлолт: mobile/API.md.</t>
-  </si>
-  <si>
-    <t>2026-09-10: /api/doctor ба /api/patient давхаргыг tests/acceptance харвалтаар туршив (248 маршрут дуудагдав, 48 бичих урсгал). Гар утасны клиент бичигдээгүй тул төгсгөл-төгсгөлийн интеграц дуусаагүй.</t>
+    <t>2026-09-10: Гар утасны API нээгдэв — /api/doctor (12 маршрут: /me, /visits, /monitoring, /advice, /reports/summary, /patients) ба /api/patient (16 маршрут: /me, /journal, /questions, /advice, /risk, /evisits, /rehab/*), server.js:373-382. Бодит HTTP төлөвийн код, жижиг үсгийн {success,message,data} бүрхүүлтэй. Гэрээний бүрэн тодорхойлолт: mobile/API.md. | 2026-09-11: /api/doctor-д 2 маршрут нэмэгдэв — GET|POST /monitoring/:patientId/questions (эмч асуултад хариулах). /api/patient/journal ба /questions бичилт засагдав (83bc3c0).</t>
+  </si>
+  <si>
+    <t>2026-09-10: /api/doctor ба /api/patient давхаргыг tests/acceptance харвалтаар туршив (248 маршрут дуудагдав, 48 бичих урсгал). Гар утасны клиент бичигдээгүй тул төгсгөл-төгсгөлийн интеграц дуусаагүй. | 2026-09-11: Гар утасны клиент mobile/app-д бий (165ce3c) — "клиент бичигдээгүй" гэсэн өмнөх тэмдэглэл хуучирсан. Тест орчинд тэмдэглэл, асуулт–хариулт, чат (үйлчлүүлэгч→эмч) урсгалыг серверийн түвшинд төгсгөл хүртэл шалгав; клиентийн засварууд mobile/CHAT-CLIENT-FIXES.md.</t>
   </si>
   <si>
     <t>Тест, чанарын баталгаажуулалт</t>
@@ -1399,7 +1399,7 @@
     <t>Өдөр тутмын бүртгэл орж, график хэлбэрээр харагдана</t>
   </si>
   <si>
-    <t>2026-09-10: Энэ дэлгэцийг тэжээх сервер тал бэлэн — GET|POST /api/patient/journal, /journal/summary (веб жагсаалтын мөр #129). Гар утасны апп-ын код бичигдээгүй тул гүйцэтгэл 0 хэвээр.</t>
+    <t>2026-09-10: Энэ дэлгэцийг тэжээх сервер тал бэлэн — GET|POST /api/patient/journal, /journal/summary (веб жагсаалтын мөр #129). Гар утасны апп-ын код бичигдээгүй тул гүйцэтгэл 0 хэвээр. | 2026-09-11: Тэмдэглэл хадгалах POST /api/patient/journal бүх оролдлогод 500 өгдөг байсныг засав — rec_status 'A' int баганад бичигдэж, id/id_group/user_mod/date_modif хоосон үлддэг байв; BaseCreate руу шилжүүлэв (commit 83bc3c0). Тест орчинд хадгалах, жагсаалтад харах бодитоор шалгагдав. Гар утасны дэлгэц mobile/app-д бий (165ce3c); төхөөрөмж дээр бид ажиллуулж шалгаагүй.</t>
   </si>
   <si>
     <t>2.3 Эмчээс асуух асуулт</t>
@@ -1411,7 +1411,7 @@
     <t>Асуулт илгээгдэж, эмчид хүрнэ</t>
   </si>
   <si>
-    <t>2026-09-10: Энэ дэлгэцийг тэжээх сервер тал бэлэн — GET|POST /api/patient/questions (веб жагсаалтын мөр #129). Гар утасны апп-ын код бичигдээгүй тул гүйцэтгэл 0 хэвээр.</t>
+    <t>2026-09-10: Энэ дэлгэцийг тэжээх сервер тал бэлэн — GET|POST /api/patient/questions (веб жагсаалтын мөр #129). Гар утасны апп-ын код бичигдээгүй тул гүйцэтгэл 0 хэвээр. | 2026-09-11: Асуулт илгээх POST /api/patient/questions 500 өгдөг байсныг засав (ижил шалтгаан, 83bc3c0). Эмч хариулах GET|POST /api/doctor/monitoring/:patientId/questions нэмэгдэв (mobile/API.md §29). Тест орчинд асуулт → эмчийн хариу → үйлчлүүлэгч эмчийн нэртэй хариугаа харах урсгал бодитоор шалгагдав. Гар утасны дэлгэц mobile/app-д бий; эмчийн модульд асуулт харах дэлгэц хараахан байхгүй (mobile/CHAT-CLIENT-FIXES.md §6).</t>
   </si>
   <si>
     <t>2.4 Эмчийн зөвлөгөө</t>
@@ -1526,6 +1526,9 @@
   </si>
   <si>
     <t>Эмч, үйлчлүүлэгч хооронд бодит цагийн харилцаа</t>
+  </si>
+  <si>
+    <t>2026-09-11: Сервер: үйлчлүүлэгч өөрийг нь хяналтад авсан эмчтэй чатлах боломжтой болов — өмнө нь зөвхөн эмчийн баг тооцогдож, тест DB-д үйлчлүүлэгчийн бичсэн мессеж 0 байв; тест орчинд StartChat амжилттай. Вэб: эмч асуултын цонхноос ("Чатаар бичих") үйлчлүүлэгчтэй чат эхлүүлэх товч нэмэгдэж, тест орчинд хөтөч дээр шалгав (MonitorQuestion.jsx). Гар утасны клиентийн чатын алдаанууд (давхар бөмбөлөг, токен дуусахад socket зогсох, татгалзал чимээгүй, "бичиж байна", хавсралт) mobile/CHAT-CLIENT-FIXES.md-д хөгжүүлэгчид шилжүүлэв.</t>
   </si>
   <si>
     <t>Мэдэгдэл (Notification)</t>
@@ -10725,849 +10728,849 @@
       </c>
       <c r="L157" s="19"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A4:L157"/>
   <conditionalFormatting sqref="H5:H157">
@@ -11635,7 +11638,7 @@
     <col min="13" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>38</v>
       </c>
@@ -12978,10 +12981,10 @@
         <v>46255</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J39" s="23">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K39" s="19" t="s">
         <v>458</v>
@@ -13016,10 +13019,10 @@
         <v>46256</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J40" s="23">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K40" s="19" t="s">
         <v>462</v>
@@ -13424,15 +13427,17 @@
         <v>46267</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J51" s="23">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K51" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="L51" s="19"/>
+      <c r="L51" s="19" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="17">
@@ -13445,10 +13450,10 @@
         <v>498</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>16</v>
@@ -13466,7 +13471,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L52" s="19"/>
     </row>
@@ -13481,10 +13486,10 @@
         <v>498</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>16</v>
@@ -13502,7 +13507,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L53" s="19"/>
     </row>
@@ -13514,13 +13519,13 @@
         <v>49</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>16</v>
@@ -13538,10 +13543,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13552,13 +13557,13 @@
         <v>49</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>16</v>
@@ -13576,10 +13581,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L55" s="19" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13590,13 +13595,13 @@
         <v>49</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>16</v>
@@ -13614,7 +13619,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L56" s="19"/>
     </row>
@@ -13626,13 +13631,13 @@
         <v>49</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>16</v>
@@ -13650,10 +13655,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13664,13 +13669,13 @@
         <v>49</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>17</v>
@@ -13688,10 +13693,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13702,13 +13707,13 @@
         <v>49</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>16</v>
@@ -13726,10 +13731,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13740,13 +13745,13 @@
         <v>49</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>16</v>
@@ -13764,10 +13769,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="19" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L60" s="19" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13778,13 +13783,13 @@
         <v>51</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>16</v>
@@ -13802,7 +13807,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L61" s="19"/>
     </row>
@@ -13814,13 +13819,13 @@
         <v>51</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>16</v>
@@ -13838,7 +13843,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L62" s="19"/>
     </row>
@@ -13850,13 +13855,13 @@
         <v>51</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>17</v>
@@ -13874,7 +13879,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L63" s="19"/>
     </row>
@@ -13886,13 +13891,13 @@
         <v>51</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>16</v>
@@ -13910,7 +13915,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L64" s="19"/>
     </row>
@@ -13922,13 +13927,13 @@
         <v>51</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>16</v>
@@ -13946,7 +13951,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L65" s="19"/>
     </row>
@@ -13958,13 +13963,13 @@
         <v>51</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>16</v>
@@ -13982,7 +13987,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L66" s="19"/>
     </row>
@@ -13994,13 +13999,13 @@
         <v>51</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>16</v>
@@ -14018,7 +14023,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="19" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L67" s="19"/>
     </row>
@@ -14030,13 +14035,13 @@
         <v>51</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>16</v>
@@ -14066,13 +14071,13 @@
         <v>53</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>16</v>
@@ -14090,7 +14095,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L69" s="19"/>
     </row>
@@ -14102,13 +14107,13 @@
         <v>53</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>16</v>
@@ -14126,7 +14131,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L70" s="19"/>
     </row>
@@ -14138,13 +14143,13 @@
         <v>53</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>17</v>
@@ -14162,7 +14167,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L71" s="19"/>
     </row>
@@ -14174,7 +14179,7 @@
         <v>53</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>264</v>
@@ -14198,7 +14203,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L72" s="19"/>
     </row>
@@ -14210,13 +14215,13 @@
         <v>53</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>268</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>17</v>
@@ -14234,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L73" s="19"/>
     </row>
@@ -14246,13 +14251,13 @@
         <v>53</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>16</v>
@@ -14270,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L74" s="19"/>
     </row>
@@ -14282,13 +14287,13 @@
         <v>55</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>17</v>
@@ -14306,7 +14311,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L75" s="19"/>
     </row>
@@ -14318,13 +14323,13 @@
         <v>55</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>16</v>
@@ -14342,7 +14347,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L76" s="19"/>
     </row>
@@ -14354,13 +14359,13 @@
         <v>55</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>16</v>
@@ -14378,7 +14383,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L77" s="19"/>
     </row>
@@ -14390,13 +14395,13 @@
         <v>55</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>16</v>
@@ -14426,13 +14431,13 @@
         <v>55</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>16</v>
@@ -14450,7 +14455,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L79" s="19"/>
     </row>
@@ -14462,13 +14467,13 @@
         <v>57</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D80" s="19" t="s">
         <v>288</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>16</v>
@@ -14486,7 +14491,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L80" s="19"/>
     </row>
@@ -14498,13 +14503,13 @@
         <v>57</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F81" s="17" t="s">
         <v>16</v>
@@ -14522,7 +14527,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L81" s="19"/>
     </row>
@@ -14534,13 +14539,13 @@
         <v>57</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F82" s="17" t="s">
         <v>16</v>
@@ -14558,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="19" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L82" s="19"/>
     </row>
@@ -14570,13 +14575,13 @@
         <v>57</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F83" s="17" t="s">
         <v>17</v>
@@ -14594,7 +14599,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="19" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L83" s="19"/>
     </row>
@@ -14606,13 +14611,13 @@
         <v>57</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D84" s="19" t="s">
         <v>304</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>17</v>
@@ -14630,7 +14635,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="19" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L84" s="19"/>
     </row>
@@ -14642,13 +14647,13 @@
         <v>57</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D85" s="19" t="s">
         <v>307</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>16</v>
@@ -14666,7 +14671,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L85" s="19"/>
     </row>
@@ -14678,13 +14683,13 @@
         <v>57</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>17</v>
@@ -14702,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="19" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L86" s="19"/>
     </row>
@@ -15688,17 +15693,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15707,33 +15712,33 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -15749,28 +15754,28 @@
         <v>1</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H7" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="8" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15778,28 +15783,28 @@
         <v>2</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>630</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>632</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>627</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>629</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>630</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>631</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>626</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>626</v>
-      </c>
-      <c r="H8" s="17" t="s">
+      <c r="I8" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="9" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15807,28 +15812,28 @@
         <v>3</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>633</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>627</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>626</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>626</v>
-      </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="10" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15836,28 +15841,28 @@
         <v>4</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H10" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I10" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="11" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15865,28 +15870,28 @@
         <v>5</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>640</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>641</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>642</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>627</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>639</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>640</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>641</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>626</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>626</v>
-      </c>
-      <c r="H11" s="17" t="s">
+      <c r="I11" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="12" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15894,28 +15899,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>643</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>644</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>642</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>627</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>643</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>641</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>626</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>626</v>
-      </c>
-      <c r="H12" s="17" t="s">
+      <c r="I12" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="13" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15923,28 +15928,28 @@
         <v>7</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>645</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>647</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>627</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>644</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>645</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>646</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>626</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>626</v>
-      </c>
-      <c r="H13" s="17" t="s">
+      <c r="I13" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="14" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15952,28 +15957,28 @@
         <v>8</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H14" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I14" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="15" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15981,28 +15986,28 @@
         <v>9</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H15" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I15" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="16" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16010,28 +16015,28 @@
         <v>10</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H16" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I16" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="17" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16042,25 +16047,25 @@
         <v>200</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H17" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I17" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="18" ht="396.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16071,25 +16076,25 @@
         <v>200</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H18" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I18" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="19" ht="396.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16097,28 +16102,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H19" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I19" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="20" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16126,28 +16131,28 @@
         <v>14</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H20" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I20" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="21" ht="85.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16155,28 +16160,28 @@
         <v>15</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H21" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I21" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="22" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16187,25 +16192,25 @@
         <v>217</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H22" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I22" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="23" ht="111.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16213,28 +16218,28 @@
         <v>17</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H23" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I23" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="24" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16242,34 +16247,34 @@
         <v>18</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H24" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="I24" s="19" t="s">
         <v>627</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="25" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -16288,25 +16293,25 @@
         <v>217</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16317,25 +16322,25 @@
         <v>217</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="29" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16346,25 +16351,25 @@
         <v>217</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="30" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16375,25 +16380,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="31" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16404,25 +16409,25 @@
         <v>217</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I31" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="32" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16433,25 +16438,25 @@
         <v>217</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="33" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16462,25 +16467,25 @@
         <v>217</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="34" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16488,28 +16493,28 @@
         <v>26</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="35" ht="111.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16517,28 +16522,28 @@
         <v>27</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="36" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16546,28 +16551,28 @@
         <v>28</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="37" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16578,25 +16583,25 @@
         <v>200</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16604,28 +16609,28 @@
         <v>30</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="39" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16633,28 +16638,28 @@
         <v>31</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="40" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16662,28 +16667,28 @@
         <v>32</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="41" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16691,28 +16696,28 @@
         <v>33</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>154</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="42" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16720,34 +16725,34 @@
         <v>34</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>326</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="43" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>

--- a/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
+++ b/МнКардио_тендерийн_ажлын_жагсаалт.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="750">
   <si>
     <t>ХЯНАЛТЫН САМБАР</t>
   </si>
@@ -1465,7 +1465,7 @@
     <t>Дасгал үзэх, гүйцэтгэлээ тэмдэглэх боломжтой</t>
   </si>
   <si>
-    <t>2026-09-10: Энэ дэлгэцийг тэжээх сервер тал бэлэн — GET /api/patient/rehab/exercises, /rehab/progress, /rehab/vitals (веб жагсаалтын мөр #129). Гар утасны апп-ын код бичигдээгүй тул гүйцэтгэл 0 хэвээр.</t>
+    <t>2026-09-10: Энэ дэлгэцийг тэжээх сервер тал бэлэн — GET /api/patient/rehab/exercises, /rehab/progress, /rehab/vitals (веб жагсаалтын мөр #129). Гар утасны апп-ын код бичигдээгүй тул гүйцэтгэл 0 хэвээр. | 2026-09-17: Дасгалын тоглуулагч бичигдэв (сонголтын хуудсаар шийдсэн хэлбэрээр) — сервер: /api/patient/rehab/today, /sessions, /checkins (backend a88b962, API.md §2.7c), MnCardio_test-д хүснэгт ба ТӨСӨЛ хөтөлбөр (add_rehab_program_tables.sql, seed_rehab_programs_draft.sql); апп: features/rehab/rehab_today_tab, rehab_player_screen, rehab_session_summary (mncardio-github feat/rehab-player 1a4b0ee). Үлдсэн: тест сервер дээр байршуулах, APK, хөтөлбөрийн агуулгыг эмнэлзүйн баг батлах.</t>
   </si>
   <si>
     <t>Телемедицин</t>
@@ -1585,6 +1585,9 @@
     <t>Зөвлөгөө, анхааруулга харагдана</t>
   </si>
   <si>
+    <t>2026-09-17: Дасгалын өмнөх зорилтот пульсын анхааруулга (RehabProgram.WarningTemplate), 2 минут тутмын пульсын өнгөт бүс, "Биеийн байдал муу байна" шинж тэмдгийн жагсаалт + 103 сануулга — rehab_player_screen.dart. Эцсийн үг хэллэгийг сэргээн засах эмч нар батлах.</t>
+  </si>
+  <si>
     <t>39 дасгалын видео бичлэг</t>
   </si>
   <si>
@@ -1618,7 +1621,7 @@
     <t>39 анимейшн бэлэн, чанарын шаардлага хангасан</t>
   </si>
   <si>
-    <t>Анимейшн хийх зардал тендерийн үнэд багтсан | 2026-09-09: Видео бичлэг хийгдээгүй тул анимейшн эхлэх боломжгүй (захидлын 9-р зүйл).</t>
+    <t>Анимейшн хийх зардал тендерийн үнэд багтсан | 2026-09-09: Видео бичлэг хийгдээгүй тул анимейшн эхлэх боломжгүй (захидлын 9-р зүйл). | 2026-09-17: Анимейшн хийх заавар, Higgsfield prompt, бичлэгийн шаардлага (9:16, 720×1280, 3–8 сек давтагдах) бэлэн — video/higgsfield-exercise-loops.md.</t>
   </si>
   <si>
     <t>Дасгалыг апп-д байршуулах</t>
@@ -1630,7 +1633,7 @@
     <t>Дасгалууд апп дотроос үзэгдэнэ</t>
   </si>
   <si>
-    <t>2026-09-09: Видео байршуулах, хүргэх шийдэл тодорхойгүй (захидлын 10-р зүйл).</t>
+    <t>2026-09-09: Видео байршуулах, хүргэх шийдэл тодорхойгүй (захидлын 10-р зүйл). | 2026-09-17: Апп-ын талд хөдөлгөөн бүрийн давтагдах бичлэг тоглуулах, урьдчилан татах, веб админд байршуулах (/admin/RehabContent, frontend 03cde63) бэлэн. Видео ирмэгц MediaRef-д холбоно.</t>
   </si>
   <si>
     <t>Админ, тайлан</t>
@@ -11638,7 +11641,7 @@
     <col min="13" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>38</v>
       </c>
@@ -13209,10 +13212,10 @@
         <v>46263</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J45" s="23">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K45" s="19" t="s">
         <v>480</v>
@@ -13613,15 +13616,17 @@
         <v>46272</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J56" s="23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K56" s="19" t="s">
         <v>520</v>
       </c>
-      <c r="L56" s="19"/>
+      <c r="L56" s="19" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="17">
@@ -13634,10 +13639,10 @@
         <v>509</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>16</v>
@@ -13655,10 +13660,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13672,10 +13677,10 @@
         <v>509</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>17</v>
@@ -13693,10 +13698,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13710,10 +13715,10 @@
         <v>509</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>16</v>
@@ -13731,10 +13736,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13748,10 +13753,10 @@
         <v>509</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>16</v>
@@ -13769,10 +13774,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="19" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L60" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -13783,13 +13788,13 @@
         <v>51</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>16</v>
@@ -13807,7 +13812,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L61" s="19"/>
     </row>
@@ -13819,13 +13824,13 @@
         <v>51</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>16</v>
@@ -13843,7 +13848,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L62" s="19"/>
     </row>
@@ -13855,13 +13860,13 @@
         <v>51</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>17</v>
@@ -13879,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="19" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L63" s="19"/>
     </row>
@@ -13891,13 +13896,13 @@
         <v>51</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>16</v>
@@ -13915,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L64" s="19"/>
     </row>
@@ -13927,13 +13932,13 @@
         <v>51</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>16</v>
@@ -13951,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L65" s="19"/>
     </row>
@@ -13963,13 +13968,13 @@
         <v>51</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>16</v>
@@ -13987,7 +13992,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L66" s="19"/>
     </row>
@@ -13999,13 +14004,13 @@
         <v>51</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>16</v>
@@ -14023,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L67" s="19"/>
     </row>
@@ -14035,13 +14040,13 @@
         <v>51</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>16</v>
@@ -14071,13 +14076,13 @@
         <v>53</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>16</v>
@@ -14095,7 +14100,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="19" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L69" s="19"/>
     </row>
@@ -14107,13 +14112,13 @@
         <v>53</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>16</v>
@@ -14131,7 +14136,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L70" s="19"/>
     </row>
@@ -14143,13 +14148,13 @@
         <v>53</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>17</v>
@@ -14167,7 +14172,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L71" s="19"/>
     </row>
@@ -14179,7 +14184,7 @@
         <v>53</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>264</v>
@@ -14203,7 +14208,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L72" s="19"/>
     </row>
@@ -14215,13 +14220,13 @@
         <v>53</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>268</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>17</v>
@@ -14239,7 +14244,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L73" s="19"/>
     </row>
@@ -14251,13 +14256,13 @@
         <v>53</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>16</v>
@@ -14275,7 +14280,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L74" s="19"/>
     </row>
@@ -14287,13 +14292,13 @@
         <v>55</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>17</v>
@@ -14311,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L75" s="19"/>
     </row>
@@ -14323,13 +14328,13 @@
         <v>55</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>16</v>
@@ -14347,7 +14352,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L76" s="19"/>
     </row>
@@ -14359,13 +14364,13 @@
         <v>55</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>16</v>
@@ -14383,7 +14388,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="19" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L77" s="19"/>
     </row>
@@ -14395,13 +14400,13 @@
         <v>55</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>16</v>
@@ -14431,13 +14436,13 @@
         <v>55</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>16</v>
@@ -14455,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L79" s="19"/>
     </row>
@@ -14467,13 +14472,13 @@
         <v>57</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D80" s="19" t="s">
         <v>288</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>16</v>
@@ -14491,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L80" s="19"/>
     </row>
@@ -14503,13 +14508,13 @@
         <v>57</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F81" s="17" t="s">
         <v>16</v>
@@ -14527,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="19" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L81" s="19"/>
     </row>
@@ -14539,13 +14544,13 @@
         <v>57</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F82" s="17" t="s">
         <v>16</v>
@@ -14563,7 +14568,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="19" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L82" s="19"/>
     </row>
@@ -14575,13 +14580,13 @@
         <v>57</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F83" s="17" t="s">
         <v>17</v>
@@ -14599,7 +14604,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="19" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L83" s="19"/>
     </row>
@@ -14611,13 +14616,13 @@
         <v>57</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D84" s="19" t="s">
         <v>304</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>17</v>
@@ -14635,7 +14640,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="19" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L84" s="19"/>
     </row>
@@ -14647,13 +14652,13 @@
         <v>57</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D85" s="19" t="s">
         <v>307</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>16</v>
@@ -14671,7 +14676,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="19" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L85" s="19"/>
     </row>
@@ -14683,13 +14688,13 @@
         <v>57</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>17</v>
@@ -14707,7 +14712,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="19" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L86" s="19"/>
     </row>
@@ -15693,17 +15698,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15712,33 +15717,33 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -15754,28 +15759,28 @@
         <v>1</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H7" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="8" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15783,28 +15788,28 @@
         <v>2</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>632</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>633</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>631</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>632</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>627</v>
-      </c>
-      <c r="H8" s="17" t="s">
+      <c r="I8" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="9" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15812,28 +15817,28 @@
         <v>3</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>636</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>633</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>635</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>627</v>
-      </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="10" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15841,28 +15846,28 @@
         <v>4</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H10" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I10" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="11" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15870,28 +15875,28 @@
         <v>5</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>641</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>642</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>640</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>641</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>642</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>627</v>
-      </c>
-      <c r="H11" s="17" t="s">
+      <c r="I11" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="12" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15899,28 +15904,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>644</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>643</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>642</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>627</v>
-      </c>
-      <c r="H12" s="17" t="s">
+      <c r="I12" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="13" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15928,28 +15933,28 @@
         <v>7</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>646</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>648</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>645</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>646</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>647</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>627</v>
-      </c>
-      <c r="H13" s="17" t="s">
+      <c r="I13" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="14" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15957,28 +15962,28 @@
         <v>8</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H14" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I14" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="15" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15986,28 +15991,28 @@
         <v>9</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H15" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I15" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="16" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16015,28 +16020,28 @@
         <v>10</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H16" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I16" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="17" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16047,25 +16052,25 @@
         <v>200</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H17" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I17" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="18" ht="396.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16076,25 +16081,25 @@
         <v>200</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H18" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I18" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="19" ht="396.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16102,28 +16107,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H19" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I19" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="20" ht="272.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16131,28 +16136,28 @@
         <v>14</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H20" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I20" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="21" ht="85.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16160,28 +16165,28 @@
         <v>15</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H21" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I21" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="22" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16192,25 +16197,25 @@
         <v>217</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H22" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I22" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="23" ht="111.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16218,28 +16223,28 @@
         <v>17</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H23" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I23" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="24" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16247,34 +16252,34 @@
         <v>18</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H24" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="I24" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="25" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -16293,25 +16298,25 @@
         <v>217</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="28" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16322,25 +16327,25 @@
         <v>217</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="29" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16351,25 +16356,25 @@
         <v>217</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16380,25 +16385,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="31" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16409,25 +16414,25 @@
         <v>217</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I31" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="32" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16438,25 +16443,25 @@
         <v>217</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16467,25 +16472,25 @@
         <v>217</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16493,28 +16498,28 @@
         <v>26</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="35" ht="111.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16522,28 +16527,28 @@
         <v>27</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="36" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16551,28 +16556,28 @@
         <v>28</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="37" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16583,25 +16588,25 @@
         <v>200</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16609,28 +16614,28 @@
         <v>30</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="39" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16638,28 +16643,28 @@
         <v>31</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="40" ht="72.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16667,28 +16672,28 @@
         <v>32</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="41" ht="59.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16696,28 +16701,28 @@
         <v>33</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>154</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="42" ht="46.7" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -16725,34 +16730,34 @@
         <v>34</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>326</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="43" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
